--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 10 close to Jul 13 close  |  503 companies  |  updated 2026-07-14 11:40</t>
+          <t>Jul 10 close to Jul 13 close  |  503 companies  |  updated 2026-07-14 11:43</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 06 close to Jul 13 close  |  503 companies  |  updated 2026-07-14 11:40</t>
+          <t>Jul 06 close to Jul 13 close  |  503 companies  |  updated 2026-07-14 11:43</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Jul 10-&gt;Jul 13) and rolling 5-day  |  updated 2026-07-14 11:40</t>
+          <t>Daily (Jul 10-&gt;Jul 13) and rolling 5-day  |  updated 2026-07-14 11:43</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 16 close to Jul 17 close  |  503 companies  |  updated 2026-07-18 03:56</t>
+          <t>Jul 16 close to Jul 17 close  |  503 companies  |  updated 2026-07-19 04:06</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>208.37</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>211.62</v>
+        <v>211.63</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>1.56</v>
@@ -2025,24 +2025,24 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>110.91</v>
+        <v>316.23</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>112.06</v>
+        <v>319.51</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>1.04</v>
@@ -2051,24 +2051,24 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>205.8</v>
+        <v>110.91</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>207.95</v>
+        <v>112.06</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>1.04</v>
@@ -2077,24 +2077,24 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>316.23</v>
+        <v>205.8</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>319.51</v>
+        <v>207.95</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>1.04</v>
@@ -2181,24 +2181,24 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>396.27</v>
+        <v>280.27</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>399.99</v>
+        <v>282.91</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -2207,24 +2207,24 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Eaton Corporation</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>280.27</v>
+        <v>396.27</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>282.91</v>
+        <v>399.99</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -2311,12 +2311,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>275.22</v>
+        <v>265.04</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>277.66</v>
+        <v>267.4</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>0.89</v>
@@ -2337,12 +2337,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>265.04</v>
+        <v>275.22</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>267.4</v>
+        <v>277.66</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>0.89</v>
@@ -2519,24 +2519,24 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>134.29</v>
+        <v>630.86</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>135.29</v>
+        <v>635.52</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>0.74</v>
@@ -2545,24 +2545,24 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>630.86</v>
+        <v>134.29</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>635.52</v>
+        <v>135.29</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>0.74</v>
@@ -2935,24 +2935,24 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Crown Castle</t>
+          <t>Oneok</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>78.73</v>
+        <v>93</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>79.17</v>
+        <v>93.52</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>0.5600000000000001</v>
@@ -2961,24 +2961,24 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Oneok</t>
+          <t>Crown Castle</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>93</v>
+        <v>78.73</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>93.52</v>
+        <v>79.17</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>0.5600000000000001</v>
@@ -3039,24 +3039,24 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Incyte</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>116.65</v>
+        <v>275.44</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>117.25</v>
+        <v>276.84</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>0.51</v>
@@ -3065,24 +3065,24 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>35.04</v>
+        <v>207.84</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>35.22</v>
+        <v>208.9</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>0.51</v>
@@ -3091,24 +3091,24 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>207.84</v>
+        <v>35.04</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>208.9</v>
+        <v>35.22</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>0.51</v>
@@ -3117,24 +3117,24 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Incyte</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>275.44</v>
+        <v>116.65</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>276.84</v>
+        <v>117.25</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>0.51</v>
@@ -3143,24 +3143,24 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>281.94</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>283.36</v>
+        <v>92</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>0.5</v>
@@ -3169,24 +3169,24 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>91.54000000000001</v>
+        <v>281.94</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>92</v>
+        <v>283.36</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>0.5</v>
@@ -3299,12 +3299,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Expeditors International</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>271.19</v>
+        <v>181.96</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>272.43</v>
+        <v>182.8</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>0.46</v>
@@ -3351,12 +3351,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Expeditors International</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>181.96</v>
+        <v>271.19</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>182.8</v>
+        <v>272.43</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>0.46</v>
@@ -3455,24 +3455,24 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>58.61</v>
+        <v>82.38</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>58.82</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>0.36</v>
@@ -3481,24 +3481,24 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>82.38</v>
+        <v>58.61</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>82.68000000000001</v>
+        <v>58.82</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>0.36</v>
@@ -3507,24 +3507,24 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>185.04</v>
+        <v>877.17</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>185.69</v>
+        <v>880.28</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>0.35</v>
@@ -3559,24 +3559,24 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>877.17</v>
+        <v>185.04</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>880.28</v>
+        <v>185.69</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>0.35</v>
@@ -3819,24 +3819,24 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Ares Management</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>188.3</v>
+        <v>125.43</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>188.68</v>
+        <v>125.68</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>0.2</v>
@@ -3845,24 +3845,24 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Ares Management</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>125.43</v>
+        <v>188.3</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>125.68</v>
+        <v>188.68</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>0.2</v>
@@ -3897,12 +3897,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>173.6</v>
+        <v>24.45</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>173.88</v>
+        <v>24.49</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>0.16</v>
@@ -3923,12 +3923,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>24.45</v>
+        <v>173.6</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>24.49</v>
+        <v>173.88</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0.16</v>
@@ -4001,24 +4001,24 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>85.29000000000001</v>
+        <v>333.26</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>85.41</v>
+        <v>333.74</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>0.14</v>
@@ -4027,24 +4027,24 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>333.26</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>333.74</v>
+        <v>85.41</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>0.14</v>
@@ -4183,12 +4183,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>168.56</v>
+        <v>211.93</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>168.61</v>
+        <v>211.99</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>0.03</v>
@@ -4209,12 +4209,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>211.93</v>
+        <v>168.56</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>211.99</v>
+        <v>168.61</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>0.03</v>
@@ -4235,24 +4235,24 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Marsh McLennan</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
-        <v>322.3</v>
+        <v>182.15</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>322.36</v>
+        <v>182.18</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>0.02</v>
@@ -4261,24 +4261,24 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Marsh McLennan</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
-        <v>182.15</v>
+        <v>322.3</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>182.18</v>
+        <v>322.36</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>0.02</v>
@@ -4287,24 +4287,24 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Williams-Sonoma, Inc.</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>841.3099999999999</v>
+        <v>228.38</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>841.39</v>
+        <v>228.41</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>0.01</v>
@@ -4313,24 +4313,24 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>228.38</v>
+        <v>841.3099999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>228.41</v>
+        <v>841.39</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>0.01</v>
@@ -4391,24 +4391,24 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Expand Energy</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>88.18000000000001</v>
+        <v>65.75</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>88.13</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F153" s="7" t="n">
         <v>-0.06</v>
@@ -4417,24 +4417,24 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Expand Energy</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>65.75</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>65.70999999999999</v>
+        <v>88.13</v>
       </c>
       <c r="F154" s="7" t="n">
         <v>-0.06</v>
@@ -4833,24 +4833,24 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Kenvue</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>19.02</v>
+        <v>154.79</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>18.98</v>
+        <v>154.46</v>
       </c>
       <c r="F170" s="7" t="n">
         <v>-0.21</v>
@@ -4859,24 +4859,24 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Kenvue</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>154.79</v>
+        <v>19.02</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>154.46</v>
+        <v>18.98</v>
       </c>
       <c r="F171" s="7" t="n">
         <v>-0.21</v>
@@ -4937,24 +4937,24 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>O’Reilly Automotive</t>
+          <t>Insulet Corporation</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>86.25</v>
+        <v>164.43</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>86.05</v>
+        <v>164.06</v>
       </c>
       <c r="F174" s="7" t="n">
         <v>-0.23</v>
@@ -4963,24 +4963,24 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Insulet Corporation</t>
+          <t>O’Reilly Automotive</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>164.43</v>
+        <v>86.25</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>164.06</v>
+        <v>86.05</v>
       </c>
       <c r="F175" s="7" t="n">
         <v>-0.23</v>
@@ -5145,24 +5145,24 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>294.33</v>
+        <v>58.56</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>293.43</v>
+        <v>58.38</v>
       </c>
       <c r="F182" s="7" t="n">
         <v>-0.31</v>
@@ -5171,24 +5171,24 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>58.56</v>
+        <v>294.33</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>58.38</v>
+        <v>293.43</v>
       </c>
       <c r="F183" s="7" t="n">
         <v>-0.31</v>
@@ -5197,24 +5197,24 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Regeneron Pharmaceuticals</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D184" s="5" t="n">
-        <v>203.76</v>
+        <v>678.9400000000001</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>203.08</v>
+        <v>676.6900000000001</v>
       </c>
       <c r="F184" s="7" t="n">
         <v>-0.33</v>
@@ -5223,24 +5223,24 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>678.9400000000001</v>
+        <v>203.76</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>676.6900000000001</v>
+        <v>203.08</v>
       </c>
       <c r="F185" s="7" t="n">
         <v>-0.33</v>
@@ -5249,24 +5249,24 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D186" s="5" t="n">
-        <v>61.49</v>
+        <v>25.14</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>61.27</v>
+        <v>25.05</v>
       </c>
       <c r="F186" s="7" t="n">
         <v>-0.36</v>
@@ -5275,24 +5275,24 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
-        <v>25.14</v>
+        <v>61.49</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>25.05</v>
+        <v>61.27</v>
       </c>
       <c r="F187" s="7" t="n">
         <v>-0.36</v>
@@ -5353,12 +5353,12 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Comfort Systems USA</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>1680.6</v>
+        <v>631.02</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>1674.06</v>
+        <v>628.53</v>
       </c>
       <c r="F190" s="7" t="n">
         <v>-0.39</v>
@@ -5379,24 +5379,24 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>Aon plc</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
-        <v>631.02</v>
+        <v>368.63</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>628.53</v>
+        <v>367.21</v>
       </c>
       <c r="F191" s="7" t="n">
         <v>-0.39</v>
@@ -5405,24 +5405,24 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Aon plc</t>
+          <t>Comfort Systems USA</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>368.63</v>
+        <v>1680.6</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>367.21</v>
+        <v>1674.06</v>
       </c>
       <c r="F192" s="7" t="n">
         <v>-0.39</v>
@@ -5691,12 +5691,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>DTE Energy</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="D203" s="5" t="n">
-        <v>43.34</v>
+        <v>148.91</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>43.13</v>
+        <v>148.19</v>
       </c>
       <c r="F203" s="7" t="n">
         <v>-0.48</v>
@@ -5717,12 +5717,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>DTE Energy</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>148.91</v>
+        <v>43.34</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>148.19</v>
+        <v>43.13</v>
       </c>
       <c r="F204" s="7" t="n">
         <v>-0.48</v>
@@ -5795,24 +5795,24 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>256.56</v>
+        <v>246.27</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>255.26</v>
+        <v>245.05</v>
       </c>
       <c r="F207" s="7" t="n">
         <v>-0.5</v>
@@ -5821,24 +5821,24 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>246.27</v>
+        <v>945.5700000000001</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>245.05</v>
+        <v>940.87</v>
       </c>
       <c r="F208" s="7" t="n">
         <v>-0.5</v>
@@ -5847,24 +5847,24 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Henry Schein</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>88.26000000000001</v>
+        <v>853.2</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>87.81999999999999</v>
+        <v>848.95</v>
       </c>
       <c r="F209" s="7" t="n">
         <v>-0.5</v>
@@ -5873,24 +5873,24 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>Henry Schein</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D210" s="5" t="n">
-        <v>945.5700000000001</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>940.87</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="F210" s="7" t="n">
         <v>-0.5</v>
@@ -5899,24 +5899,24 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>853.2</v>
+        <v>256.56</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>848.95</v>
+        <v>255.27</v>
       </c>
       <c r="F211" s="7" t="n">
         <v>-0.5</v>
@@ -5951,24 +5951,24 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Parker Hannifin</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
-        <v>958.34</v>
+        <v>78.05</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>953.21</v>
+        <v>77.63</v>
       </c>
       <c r="F213" s="7" t="n">
         <v>-0.54</v>
@@ -5977,24 +5977,24 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Parker Hannifin</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D214" s="5" t="n">
-        <v>78.05</v>
+        <v>958.34</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>77.63</v>
+        <v>953.21</v>
       </c>
       <c r="F214" s="7" t="n">
         <v>-0.54</v>
@@ -6003,24 +6003,24 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>Air Products</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
-        <v>75.04000000000001</v>
+        <v>297.29</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>74.62</v>
+        <v>295.62</v>
       </c>
       <c r="F215" s="7" t="n">
         <v>-0.5600000000000001</v>
@@ -6029,24 +6029,24 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Air Products</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D216" s="5" t="n">
-        <v>297.29</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>295.62</v>
+        <v>74.62</v>
       </c>
       <c r="F216" s="7" t="n">
         <v>-0.5600000000000001</v>
@@ -6055,24 +6055,24 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
-        <v>250.99</v>
+        <v>141.26</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>249.56</v>
+        <v>140.46</v>
       </c>
       <c r="F217" s="7" t="n">
         <v>-0.57</v>
@@ -6081,24 +6081,24 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D218" s="5" t="n">
-        <v>141.26</v>
+        <v>250.99</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>140.46</v>
+        <v>249.56</v>
       </c>
       <c r="F218" s="7" t="n">
         <v>-0.57</v>
@@ -6107,24 +6107,24 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Technologies</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>226.33</v>
+        <v>205.01</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>225.02</v>
+        <v>203.83</v>
       </c>
       <c r="F219" s="7" t="n">
         <v>-0.58</v>
@@ -6159,24 +6159,24 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Honeywell Technologies</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>205.01</v>
+        <v>226.33</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>203.83</v>
+        <v>225.02</v>
       </c>
       <c r="F221" s="7" t="n">
         <v>-0.58</v>
@@ -6237,24 +6237,24 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D224" s="5" t="n">
-        <v>114.95</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>114.24</v>
+        <v>88.8</v>
       </c>
       <c r="F224" s="7" t="n">
         <v>-0.62</v>
@@ -6263,24 +6263,24 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
-        <v>89.34999999999999</v>
+        <v>114.95</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>88.8</v>
+        <v>114.24</v>
       </c>
       <c r="F225" s="7" t="n">
         <v>-0.62</v>
@@ -6341,24 +6341,24 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Hasbro</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D228" s="5" t="n">
-        <v>82.09</v>
+        <v>43.88</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>81.55</v>
+        <v>43.59</v>
       </c>
       <c r="F228" s="7" t="n">
         <v>-0.66</v>
@@ -6367,24 +6367,24 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Hasbro</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
-        <v>43.88</v>
+        <v>82.09</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>43.59</v>
+        <v>81.55</v>
       </c>
       <c r="F229" s="7" t="n">
         <v>-0.66</v>
@@ -6575,24 +6575,24 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>Kinder Morgan</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
-        <v>45.7</v>
+        <v>32.54</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>45.36</v>
+        <v>32.3</v>
       </c>
       <c r="F237" s="7" t="n">
         <v>-0.74</v>
@@ -6601,24 +6601,24 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Kinder Morgan</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D238" s="5" t="n">
-        <v>32.54</v>
+        <v>133.13</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>32.3</v>
+        <v>132.14</v>
       </c>
       <c r="F238" s="7" t="n">
         <v>-0.74</v>
@@ -6653,24 +6653,24 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>133.13</v>
+        <v>45.7</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>132.14</v>
+        <v>45.36</v>
       </c>
       <c r="F240" s="7" t="n">
         <v>-0.74</v>
@@ -6705,24 +6705,24 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D242" s="5" t="n">
-        <v>21.98</v>
+        <v>45.46</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>21.81</v>
+        <v>45.11</v>
       </c>
       <c r="F242" s="7" t="n">
         <v>-0.77</v>
@@ -6731,24 +6731,24 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
-        <v>45.46</v>
+        <v>21.98</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>45.11</v>
+        <v>21.81</v>
       </c>
       <c r="F243" s="7" t="n">
         <v>-0.77</v>
@@ -6783,12 +6783,12 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>169.7</v>
+        <v>255.93</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>168.36</v>
+        <v>253.9</v>
       </c>
       <c r="F245" s="7" t="n">
         <v>-0.79</v>
@@ -6809,12 +6809,12 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>255.93</v>
+        <v>169.7</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>253.9</v>
+        <v>168.36</v>
       </c>
       <c r="F246" s="7" t="n">
         <v>-0.79</v>
@@ -7043,24 +7043,24 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>206.25</v>
+        <v>126.11</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>204.45</v>
+        <v>125.01</v>
       </c>
       <c r="F255" s="7" t="n">
         <v>-0.87</v>
@@ -7069,24 +7069,24 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>126.11</v>
+        <v>206.25</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>125.01</v>
+        <v>204.45</v>
       </c>
       <c r="F256" s="7" t="n">
         <v>-0.87</v>
@@ -7147,24 +7147,24 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>News Corp (Class A)</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>71.69</v>
+        <v>28.69</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>71.04000000000001</v>
+        <v>28.43</v>
       </c>
       <c r="F259" s="7" t="n">
         <v>-0.91</v>
@@ -7173,24 +7173,24 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>News Corp (Class A)</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D260" s="5" t="n">
-        <v>28.69</v>
+        <v>71.69</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>28.43</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="F260" s="7" t="n">
         <v>-0.91</v>
@@ -7199,24 +7199,24 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>255.2</v>
+        <v>513.52</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>252.86</v>
+        <v>508.77</v>
       </c>
       <c r="F261" s="7" t="n">
         <v>-0.92</v>
@@ -7225,24 +7225,24 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D262" s="5" t="n">
-        <v>513.52</v>
+        <v>255.2</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>508.77</v>
+        <v>252.86</v>
       </c>
       <c r="F262" s="7" t="n">
         <v>-0.92</v>
@@ -7329,24 +7329,24 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D266" s="5" t="n">
-        <v>374.45</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>370.82</v>
+        <v>92.25</v>
       </c>
       <c r="F266" s="7" t="n">
         <v>-0.97</v>
@@ -7355,24 +7355,24 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
-        <v>93.15000000000001</v>
+        <v>374.45</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>92.25</v>
+        <v>370.83</v>
       </c>
       <c r="F267" s="7" t="n">
         <v>-0.97</v>
@@ -7459,24 +7459,24 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Gen Digital</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
-        <v>533.21</v>
+        <v>27.01</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>527.87</v>
+        <v>26.74</v>
       </c>
       <c r="F271" s="7" t="n">
         <v>-1</v>
@@ -7485,24 +7485,24 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>114.49</v>
+        <v>151.5</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>113.35</v>
+        <v>149.98</v>
       </c>
       <c r="F272" s="7" t="n">
         <v>-1</v>
@@ -7511,24 +7511,24 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>151.5</v>
+        <v>114.49</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>149.98</v>
+        <v>113.35</v>
       </c>
       <c r="F273" s="7" t="n">
         <v>-1</v>
@@ -7537,24 +7537,24 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Gen Digital</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D274" s="5" t="n">
-        <v>27.01</v>
+        <v>533.21</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>26.74</v>
+        <v>527.87</v>
       </c>
       <c r="F274" s="7" t="n">
         <v>-1</v>
@@ -7589,24 +7589,24 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Vici Properties</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D276" s="5" t="n">
-        <v>500.94</v>
+        <v>27.15</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>495.76</v>
+        <v>26.87</v>
       </c>
       <c r="F276" s="7" t="n">
         <v>-1.03</v>
@@ -7615,24 +7615,24 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Vici Properties</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>27.15</v>
+        <v>500.94</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>26.87</v>
+        <v>495.76</v>
       </c>
       <c r="F277" s="7" t="n">
         <v>-1.03</v>
@@ -7719,24 +7719,24 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
-        <v>99.12</v>
+        <v>249.89</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>247.23</v>
       </c>
       <c r="F281" s="7" t="n">
         <v>-1.06</v>
@@ -7771,24 +7771,24 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>249.89</v>
+        <v>99.12</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>247.23</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F283" s="7" t="n">
         <v>-1.06</v>
@@ -7875,24 +7875,24 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
-        <v>118.68</v>
+        <v>127.16</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>117.36</v>
+        <v>125.75</v>
       </c>
       <c r="F287" s="7" t="n">
         <v>-1.11</v>
@@ -7901,24 +7901,24 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D288" s="5" t="n">
-        <v>127.16</v>
+        <v>118.68</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>125.75</v>
+        <v>117.36</v>
       </c>
       <c r="F288" s="7" t="n">
         <v>-1.11</v>
@@ -7979,24 +7979,24 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>70.65000000000001</v>
+        <v>46.79</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>69.84999999999999</v>
+        <v>46.26</v>
       </c>
       <c r="F291" s="7" t="n">
         <v>-1.13</v>
@@ -8005,24 +8005,24 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D292" s="5" t="n">
-        <v>46.79</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>46.26</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="F292" s="7" t="n">
         <v>-1.13</v>
@@ -8031,24 +8031,24 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>94.06999999999999</v>
+        <v>362.44</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>92.98</v>
+        <v>358.24</v>
       </c>
       <c r="F293" s="7" t="n">
         <v>-1.16</v>
@@ -8057,24 +8057,24 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>362.44</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>358.24</v>
+        <v>92.98</v>
       </c>
       <c r="F294" s="7" t="n">
         <v>-1.16</v>
@@ -8265,24 +8265,24 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>75.75</v>
+        <v>147.8</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>74.81999999999999</v>
+        <v>145.98</v>
       </c>
       <c r="F302" s="7" t="n">
         <v>-1.23</v>
@@ -8291,24 +8291,24 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
-        <v>147.8</v>
+        <v>75.75</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>145.98</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="F303" s="7" t="n">
         <v>-1.23</v>
@@ -8317,24 +8317,24 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Hormel Foods</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D304" s="5" t="n">
-        <v>25.71</v>
+        <v>90.83</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>25.39</v>
+        <v>89.7</v>
       </c>
       <c r="F304" s="7" t="n">
         <v>-1.24</v>
@@ -8343,24 +8343,24 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Hormel Foods</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
-        <v>90.83</v>
+        <v>25.71</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>89.7</v>
+        <v>25.39</v>
       </c>
       <c r="F305" s="7" t="n">
         <v>-1.24</v>
@@ -8577,24 +8577,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Kraft Heinz</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>26.23</v>
+        <v>201.21</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>25.88</v>
+        <v>198.53</v>
       </c>
       <c r="F314" s="7" t="n">
         <v>-1.33</v>
@@ -8603,24 +8603,24 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Kraft Heinz</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
-        <v>201.21</v>
+        <v>26.23</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>198.53</v>
+        <v>25.88</v>
       </c>
       <c r="F315" s="7" t="n">
         <v>-1.33</v>
@@ -8733,24 +8733,24 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>1087.05</v>
+        <v>113.1</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>1072.2</v>
+        <v>111.55</v>
       </c>
       <c r="F320" s="7" t="n">
         <v>-1.37</v>
@@ -8759,24 +8759,24 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>113.1</v>
+        <v>1087.05</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>111.55</v>
+        <v>1072.2</v>
       </c>
       <c r="F321" s="7" t="n">
         <v>-1.37</v>
@@ -8863,24 +8863,24 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D325" s="5" t="n">
-        <v>237.15</v>
+        <v>114.57</v>
       </c>
       <c r="E325" s="5" t="n">
-        <v>233.84</v>
+        <v>112.97</v>
       </c>
       <c r="F325" s="7" t="n">
         <v>-1.4</v>
@@ -8889,24 +8889,24 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D326" s="5" t="n">
-        <v>114.57</v>
+        <v>237.15</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>112.97</v>
+        <v>233.84</v>
       </c>
       <c r="F326" s="7" t="n">
         <v>-1.4</v>
@@ -8915,24 +8915,24 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>134.86</v>
+        <v>179.62</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>132.96</v>
+        <v>177.08</v>
       </c>
       <c r="F327" s="7" t="n">
         <v>-1.41</v>
@@ -8941,24 +8941,24 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>179.62</v>
+        <v>153.84</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>177.08</v>
+        <v>151.67</v>
       </c>
       <c r="F328" s="7" t="n">
         <v>-1.41</v>
@@ -8967,24 +8967,24 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>153.84</v>
+        <v>134.86</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>151.67</v>
+        <v>132.96</v>
       </c>
       <c r="F329" s="7" t="n">
         <v>-1.41</v>
@@ -9071,24 +9071,24 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PNW</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Pinnacle West Capital</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>457.38</v>
+        <v>109.29</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>450.84</v>
+        <v>107.73</v>
       </c>
       <c r="F333" s="7" t="n">
         <v>-1.43</v>
@@ -9123,24 +9123,24 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Pinnacle West Capital</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>109.29</v>
+        <v>457.38</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>107.73</v>
+        <v>450.84</v>
       </c>
       <c r="F335" s="7" t="n">
         <v>-1.43</v>
@@ -9149,24 +9149,24 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>520.74</v>
+        <v>551.54</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>513.22</v>
+        <v>543.6</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>-1.44</v>
@@ -9175,24 +9175,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D337" s="5" t="n">
-        <v>551.54</v>
+        <v>520.74</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>543.6</v>
+        <v>513.22</v>
       </c>
       <c r="F337" s="7" t="n">
         <v>-1.44</v>
@@ -9253,24 +9253,24 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>BF.B</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>PPL Corporation</t>
+          <t>Brown–Forman</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D340" s="5" t="n">
-        <v>36.38</v>
+        <v>25.96</v>
       </c>
       <c r="E340" s="5" t="n">
-        <v>35.85</v>
+        <v>25.58</v>
       </c>
       <c r="F340" s="7" t="n">
         <v>-1.46</v>
@@ -9279,24 +9279,24 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>BF.B</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>Brown–Forman</t>
+          <t>PPL Corporation</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>25.96</v>
+        <v>36.38</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>25.58</v>
+        <v>35.85</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>-1.46</v>
@@ -9435,24 +9435,24 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>98.11</v>
+        <v>31.38</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>96.64</v>
+        <v>30.91</v>
       </c>
       <c r="F347" s="7" t="n">
         <v>-1.5</v>
@@ -9461,24 +9461,24 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D348" s="5" t="n">
-        <v>31.38</v>
+        <v>98.11</v>
       </c>
       <c r="E348" s="5" t="n">
-        <v>30.91</v>
+        <v>96.64</v>
       </c>
       <c r="F348" s="7" t="n">
         <v>-1.5</v>
@@ -9513,24 +9513,24 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Essex Property Trust</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D350" s="5" t="n">
-        <v>79.98</v>
+        <v>297.42</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>78.77</v>
+        <v>292.93</v>
       </c>
       <c r="F350" s="7" t="n">
         <v>-1.51</v>
@@ -9539,24 +9539,24 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>Essex Property Trust</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>297.42</v>
+        <v>79.98</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>292.93</v>
+        <v>78.77</v>
       </c>
       <c r="F351" s="7" t="n">
         <v>-1.51</v>
@@ -9617,24 +9617,24 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>Dover Corporation</t>
+          <t>Palantir Technologies</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D354" s="5" t="n">
-        <v>217.51</v>
+        <v>134.44</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>214.18</v>
+        <v>132.38</v>
       </c>
       <c r="F354" s="7" t="n">
         <v>-1.53</v>
@@ -9643,24 +9643,24 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Palantir Technologies</t>
+          <t>Dover Corporation</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>134.44</v>
+        <v>217.51</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>132.38</v>
+        <v>214.18</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>-1.53</v>
@@ -9669,24 +9669,24 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D356" s="5" t="n">
-        <v>121.12</v>
+        <v>27.29</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>119.25</v>
+        <v>26.87</v>
       </c>
       <c r="F356" s="7" t="n">
         <v>-1.54</v>
@@ -9695,24 +9695,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>27.29</v>
+        <v>121.12</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>26.87</v>
+        <v>119.25</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>-1.54</v>
@@ -9851,24 +9851,24 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>139.48</v>
+        <v>277.89</v>
       </c>
       <c r="E363" s="5" t="n">
-        <v>137.24</v>
+        <v>273.41</v>
       </c>
       <c r="F363" s="7" t="n">
         <v>-1.61</v>
@@ -9877,24 +9877,24 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D364" s="5" t="n">
-        <v>277.89</v>
+        <v>31.01</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>273.41</v>
+        <v>30.51</v>
       </c>
       <c r="F364" s="7" t="n">
         <v>-1.61</v>
@@ -9903,24 +9903,24 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D365" s="5" t="n">
-        <v>31.01</v>
+        <v>139.48</v>
       </c>
       <c r="E365" s="5" t="n">
-        <v>30.51</v>
+        <v>137.24</v>
       </c>
       <c r="F365" s="7" t="n">
         <v>-1.61</v>
@@ -10059,12 +10059,12 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>FactSet</t>
+          <t>Huntington Bancshares</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="D371" s="5" t="n">
-        <v>262.46</v>
+        <v>18.56</v>
       </c>
       <c r="E371" s="5" t="n">
-        <v>258.09</v>
+        <v>18.25</v>
       </c>
       <c r="F371" s="7" t="n">
         <v>-1.67</v>
@@ -10085,24 +10085,24 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>FactSet</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D372" s="5" t="n">
-        <v>108.29</v>
+        <v>262.46</v>
       </c>
       <c r="E372" s="5" t="n">
-        <v>106.48</v>
+        <v>258.09</v>
       </c>
       <c r="F372" s="7" t="n">
         <v>-1.67</v>
@@ -10111,24 +10111,24 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>Fidelity National Information Services</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D373" s="5" t="n">
-        <v>42.62</v>
+        <v>108.29</v>
       </c>
       <c r="E373" s="5" t="n">
-        <v>41.91</v>
+        <v>106.48</v>
       </c>
       <c r="F373" s="7" t="n">
         <v>-1.67</v>
@@ -10137,12 +10137,12 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>Huntington Bancshares</t>
+          <t>Fidelity National Information Services</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>18.56</v>
+        <v>42.62</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>18.25</v>
+        <v>41.91</v>
       </c>
       <c r="F374" s="7" t="n">
         <v>-1.67</v>
@@ -10241,24 +10241,24 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>J.M. Smucker Company (The)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D378" s="5" t="n">
-        <v>113.97</v>
+        <v>361.57</v>
       </c>
       <c r="E378" s="5" t="n">
-        <v>112.01</v>
+        <v>355.35</v>
       </c>
       <c r="F378" s="7" t="n">
         <v>-1.72</v>
@@ -10267,24 +10267,24 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>J.M. Smucker Company (The)</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D379" s="5" t="n">
-        <v>361.57</v>
+        <v>113.97</v>
       </c>
       <c r="E379" s="5" t="n">
-        <v>355.35</v>
+        <v>112.01</v>
       </c>
       <c r="F379" s="7" t="n">
         <v>-1.72</v>
@@ -10371,24 +10371,24 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Company (The)</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D383" s="5" t="n">
-        <v>22.53</v>
+        <v>131.71</v>
       </c>
       <c r="E383" s="5" t="n">
-        <v>22.13</v>
+        <v>129.36</v>
       </c>
       <c r="F383" s="7" t="n">
         <v>-1.78</v>
@@ -10397,24 +10397,24 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Mosaic Company (The)</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D384" s="5" t="n">
-        <v>131.71</v>
+        <v>22.53</v>
       </c>
       <c r="E384" s="5" t="n">
-        <v>129.36</v>
+        <v>22.13</v>
       </c>
       <c r="F384" s="7" t="n">
         <v>-1.78</v>
@@ -10475,24 +10475,24 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>Nike, Inc.</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D387" s="5" t="n">
-        <v>92.20999999999999</v>
+        <v>44.57</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>90.53</v>
+        <v>43.76</v>
       </c>
       <c r="F387" s="7" t="n">
         <v>-1.82</v>
@@ -10501,24 +10501,24 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D388" s="5" t="n">
-        <v>401.1</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="E388" s="5" t="n">
-        <v>393.82</v>
+        <v>90.53</v>
       </c>
       <c r="F388" s="7" t="n">
         <v>-1.82</v>
@@ -10527,24 +10527,24 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Nike, Inc.</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>44.57</v>
+        <v>401.1</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>43.76</v>
+        <v>393.82</v>
       </c>
       <c r="F389" s="7" t="n">
         <v>-1.82</v>
@@ -10605,24 +10605,24 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>ResMed</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D392" s="5" t="n">
-        <v>202.76</v>
+        <v>80.14</v>
       </c>
       <c r="E392" s="5" t="n">
-        <v>198.99</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="F392" s="7" t="n">
         <v>-1.86</v>
@@ -10631,24 +10631,24 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>ResMed</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>80.14</v>
+        <v>202.76</v>
       </c>
       <c r="E393" s="5" t="n">
-        <v>78.65000000000001</v>
+        <v>198.99</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>-1.86</v>
@@ -10683,12 +10683,12 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Hershey Company (The)</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
@@ -10697,10 +10697,10 @@
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>38.7</v>
+        <v>174.72</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>37.97</v>
+        <v>171.42</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>-1.89</v>
@@ -10735,24 +10735,24 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>Hershey Company (The)</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D397" s="5" t="n">
-        <v>174.72</v>
+        <v>142.89</v>
       </c>
       <c r="E397" s="5" t="n">
-        <v>171.42</v>
+        <v>140.19</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>-1.89</v>
@@ -10761,24 +10761,24 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D398" s="5" t="n">
-        <v>142.89</v>
+        <v>38.7</v>
       </c>
       <c r="E398" s="5" t="n">
-        <v>140.19</v>
+        <v>37.97</v>
       </c>
       <c r="F398" s="7" t="n">
         <v>-1.89</v>
@@ -10813,24 +10813,24 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>CBRE Group</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D400" s="5" t="n">
-        <v>143.69</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E400" s="5" t="n">
-        <v>140.96</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="F400" s="7" t="n">
         <v>-1.9</v>
@@ -10839,24 +10839,24 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>CBRE Group</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D401" s="5" t="n">
-        <v>73.09999999999999</v>
+        <v>143.69</v>
       </c>
       <c r="E401" s="5" t="n">
-        <v>71.70999999999999</v>
+        <v>140.96</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>-1.9</v>
@@ -11151,24 +11151,24 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>125.3</v>
+        <v>44.84</v>
       </c>
       <c r="E413" s="5" t="n">
-        <v>122.78</v>
+        <v>43.94</v>
       </c>
       <c r="F413" s="7" t="n">
         <v>-2.01</v>
@@ -11203,24 +11203,24 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>44.84</v>
+        <v>125.3</v>
       </c>
       <c r="E415" s="5" t="n">
-        <v>43.94</v>
+        <v>122.78</v>
       </c>
       <c r="F415" s="7" t="n">
         <v>-2.01</v>
@@ -11385,24 +11385,24 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>Lululemon Athletica</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D422" s="5" t="n">
-        <v>75</v>
+        <v>118.79</v>
       </c>
       <c r="E422" s="5" t="n">
-        <v>73.45</v>
+        <v>116.33</v>
       </c>
       <c r="F422" s="7" t="n">
         <v>-2.07</v>
@@ -11411,24 +11411,24 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>Lululemon Athletica</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D423" s="5" t="n">
-        <v>118.79</v>
+        <v>75</v>
       </c>
       <c r="E423" s="5" t="n">
-        <v>116.33</v>
+        <v>73.45</v>
       </c>
       <c r="F423" s="7" t="n">
         <v>-2.07</v>
@@ -11437,24 +11437,24 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D424" s="5" t="n">
-        <v>135.72</v>
+        <v>273.46</v>
       </c>
       <c r="E424" s="5" t="n">
-        <v>132.87</v>
+        <v>267.71</v>
       </c>
       <c r="F424" s="7" t="n">
         <v>-2.1</v>
@@ -11463,24 +11463,24 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>Franklin Resources</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>33.33</v>
+        <v>135.72</v>
       </c>
       <c r="E425" s="5" t="n">
-        <v>32.63</v>
+        <v>132.87</v>
       </c>
       <c r="F425" s="7" t="n">
         <v>-2.1</v>
@@ -11489,24 +11489,24 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D426" s="5" t="n">
-        <v>229.16</v>
+        <v>160.49</v>
       </c>
       <c r="E426" s="5" t="n">
-        <v>224.35</v>
+        <v>157.12</v>
       </c>
       <c r="F426" s="7" t="n">
         <v>-2.1</v>
@@ -11515,12 +11515,12 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Franklin Resources</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="D427" s="5" t="n">
-        <v>160.49</v>
+        <v>33.33</v>
       </c>
       <c r="E427" s="5" t="n">
-        <v>157.12</v>
+        <v>32.63</v>
       </c>
       <c r="F427" s="7" t="n">
         <v>-2.1</v>
@@ -11541,24 +11541,24 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D428" s="5" t="n">
-        <v>273.46</v>
+        <v>229.16</v>
       </c>
       <c r="E428" s="5" t="n">
-        <v>267.71</v>
+        <v>224.35</v>
       </c>
       <c r="F428" s="7" t="n">
         <v>-2.1</v>
@@ -11567,24 +11567,24 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>51.72</v>
+        <v>63.15</v>
       </c>
       <c r="E429" s="5" t="n">
-        <v>50.63</v>
+        <v>61.82</v>
       </c>
       <c r="F429" s="7" t="n">
         <v>-2.11</v>
@@ -11593,24 +11593,24 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D430" s="5" t="n">
-        <v>63.15</v>
+        <v>51.72</v>
       </c>
       <c r="E430" s="5" t="n">
-        <v>61.82</v>
+        <v>50.63</v>
       </c>
       <c r="F430" s="7" t="n">
         <v>-2.11</v>
@@ -11671,12 +11671,12 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
       <c r="C433" s="4" t="inlineStr">
@@ -11685,10 +11685,10 @@
         </is>
       </c>
       <c r="D433" s="5" t="n">
-        <v>354.46</v>
+        <v>353.81</v>
       </c>
       <c r="E433" s="5" t="n">
-        <v>346.77</v>
+        <v>346.12</v>
       </c>
       <c r="F433" s="7" t="n">
         <v>-2.17</v>
@@ -11697,12 +11697,12 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class C)</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C434" s="4" t="inlineStr">
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="D434" s="5" t="n">
-        <v>353.81</v>
+        <v>354.46</v>
       </c>
       <c r="E434" s="5" t="n">
-        <v>346.12</v>
+        <v>346.77</v>
       </c>
       <c r="F434" s="7" t="n">
         <v>-2.17</v>
@@ -11775,24 +11775,24 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>McCormick &amp; Company</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D437" s="5" t="n">
-        <v>52.9</v>
+        <v>329.67</v>
       </c>
       <c r="E437" s="5" t="n">
-        <v>51.7</v>
+        <v>322.18</v>
       </c>
       <c r="F437" s="7" t="n">
         <v>-2.27</v>
@@ -11801,24 +11801,24 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>McCormick &amp; Company</t>
         </is>
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D438" s="5" t="n">
-        <v>329.67</v>
+        <v>52.9</v>
       </c>
       <c r="E438" s="5" t="n">
-        <v>322.18</v>
+        <v>51.7</v>
       </c>
       <c r="F438" s="7" t="n">
         <v>-2.27</v>
@@ -11957,24 +11957,24 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>Apollo Global Management</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D444" s="5" t="n">
-        <v>123.34</v>
+        <v>109.03</v>
       </c>
       <c r="E444" s="5" t="n">
-        <v>120.47</v>
+        <v>106.49</v>
       </c>
       <c r="F444" s="7" t="n">
         <v>-2.33</v>
@@ -11983,24 +11983,24 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D445" s="5" t="n">
-        <v>109.03</v>
+        <v>123.34</v>
       </c>
       <c r="E445" s="5" t="n">
-        <v>106.49</v>
+        <v>120.47</v>
       </c>
       <c r="F445" s="7" t="n">
         <v>-2.33</v>
@@ -12139,24 +12139,24 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Copart</t>
         </is>
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D451" s="5" t="n">
-        <v>87.84</v>
+        <v>28.29</v>
       </c>
       <c r="E451" s="5" t="n">
-        <v>85.73</v>
+        <v>27.61</v>
       </c>
       <c r="F451" s="7" t="n">
         <v>-2.4</v>
@@ -12165,24 +12165,24 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>Copart</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D452" s="5" t="n">
-        <v>28.29</v>
+        <v>87.84</v>
       </c>
       <c r="E452" s="5" t="n">
-        <v>27.61</v>
+        <v>85.73</v>
       </c>
       <c r="F452" s="7" t="n">
         <v>-2.4</v>
@@ -12659,24 +12659,24 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>Trade Desk (The)</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D471" s="5" t="n">
-        <v>19.12</v>
+        <v>94.25</v>
       </c>
       <c r="E471" s="5" t="n">
-        <v>18.59</v>
+        <v>91.64</v>
       </c>
       <c r="F471" s="7" t="n">
         <v>-2.77</v>
@@ -12685,24 +12685,24 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Trade Desk (The)</t>
         </is>
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D472" s="5" t="n">
-        <v>94.25</v>
+        <v>19.12</v>
       </c>
       <c r="E472" s="5" t="n">
-        <v>91.64</v>
+        <v>18.59</v>
       </c>
       <c r="F472" s="7" t="n">
         <v>-2.77</v>
@@ -12945,24 +12945,24 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D482" s="5" t="n">
-        <v>219.37</v>
+        <v>59.26</v>
       </c>
       <c r="E482" s="5" t="n">
-        <v>212.75</v>
+        <v>57.47</v>
       </c>
       <c r="F482" s="7" t="n">
         <v>-3.02</v>
@@ -12971,24 +12971,24 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D483" s="5" t="n">
-        <v>59.26</v>
+        <v>219.37</v>
       </c>
       <c r="E483" s="5" t="n">
-        <v>57.47</v>
+        <v>212.75</v>
       </c>
       <c r="F483" s="7" t="n">
         <v>-3.02</v>
@@ -13534,7 +13534,7 @@
         <v>417.03</v>
       </c>
       <c r="E504" s="5" t="n">
-        <v>384.27</v>
+        <v>384.28</v>
       </c>
       <c r="F504" s="7" t="n">
         <v>-7.85</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 10 close to Jul 17 close  |  503 companies  |  updated 2026-07-18 03:56</t>
+          <t>Jul 10 close to Jul 17 close  |  503 companies  |  updated 2026-07-19 04:06</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14716,7 @@
         <v>241.92</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>255.26</v>
+        <v>255.27</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>256.56</v>
@@ -15755,30 +15755,30 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Federal Realty Investment Trust</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>138.95</v>
+        <v>120.94</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>144.78</v>
+        <v>126.02</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>145.43</v>
+        <v>126.02</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>138.95</v>
+        <v>120.94</v>
       </c>
       <c r="H69" s="6" t="n">
         <v>4.2</v>
@@ -15787,30 +15787,30 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>120.94</v>
+        <v>138.95</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>126.02</v>
+        <v>144.78</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>126.02</v>
+        <v>145.43</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>120.94</v>
+        <v>138.95</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>4.2</v>
@@ -16619,12 +16619,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Gilead Sciences</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -16633,16 +16633,16 @@
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>129.83</v>
+        <v>199.15</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>134.28</v>
+        <v>205.99</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>136.3</v>
+        <v>209.03</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>129.83</v>
+        <v>191.95</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>3.43</v>
@@ -16651,12 +16651,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Gilead Sciences</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -16665,16 +16665,16 @@
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>199.15</v>
+        <v>129.83</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>205.99</v>
+        <v>134.28</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>209.03</v>
+        <v>136.3</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>191.95</v>
+        <v>129.83</v>
       </c>
       <c r="H97" s="6" t="n">
         <v>3.43</v>
@@ -17099,30 +17099,30 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Prudential Financial</t>
+          <t>Merck &amp; Co.</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>115.37</v>
+        <v>123.54</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>119.07</v>
+        <v>127.5</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>119.07</v>
+        <v>127.63</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>114.79</v>
+        <v>120.78</v>
       </c>
       <c r="H111" s="6" t="n">
         <v>3.21</v>
@@ -17131,30 +17131,30 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Merck &amp; Co.</t>
+          <t>Prudential Financial</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>123.54</v>
+        <v>115.37</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>127.5</v>
+        <v>119.07</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>127.63</v>
+        <v>119.07</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>120.78</v>
+        <v>114.79</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>3.21</v>
@@ -17163,30 +17163,30 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Gen Digital</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>526.74</v>
+        <v>25.91</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>543.6</v>
+        <v>26.74</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>551.54</v>
+        <v>27.01</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>526.74</v>
+        <v>25.91</v>
       </c>
       <c r="H113" s="6" t="n">
         <v>3.2</v>
@@ -17195,30 +17195,30 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Gen Digital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>25.91</v>
+        <v>526.74</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>26.74</v>
+        <v>543.6</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>27.01</v>
+        <v>551.54</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>25.91</v>
+        <v>526.74</v>
       </c>
       <c r="H114" s="6" t="n">
         <v>3.2</v>
@@ -17355,30 +17355,30 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Steel Dynamics</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>123.09</v>
+        <v>228.42</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>126.91</v>
+        <v>235.51</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>128.97</v>
+        <v>235.56</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>122.04</v>
+        <v>228.42</v>
       </c>
       <c r="H119" s="6" t="n">
         <v>3.1</v>
@@ -17387,30 +17387,30 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Steel Dynamics</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>228.42</v>
+        <v>123.09</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>235.51</v>
+        <v>126.91</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>235.56</v>
+        <v>128.97</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>228.42</v>
+        <v>122.04</v>
       </c>
       <c r="H120" s="6" t="n">
         <v>3.1</v>
@@ -18059,30 +18059,30 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>HP Inc.</t>
+          <t>Waste Management</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>24.22</v>
+        <v>233.33</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>24.84</v>
+        <v>239.31</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>24.84</v>
+        <v>242.25</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>23.75</v>
+        <v>232.8</v>
       </c>
       <c r="H141" s="6" t="n">
         <v>2.56</v>
@@ -18123,30 +18123,30 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Waste Management</t>
+          <t>HP Inc.</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>233.33</v>
+        <v>24.22</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>239.31</v>
+        <v>24.84</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>242.25</v>
+        <v>24.84</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>232.8</v>
+        <v>23.75</v>
       </c>
       <c r="H143" s="6" t="n">
         <v>2.56</v>
@@ -18507,30 +18507,30 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>469.2</v>
+        <v>88.22</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>479.57</v>
+        <v>90.17</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>479.57</v>
+        <v>91.31</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>466.14</v>
+        <v>86.53</v>
       </c>
       <c r="H155" s="6" t="n">
         <v>2.21</v>
@@ -18539,30 +18539,30 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
-        <v>88.22</v>
+        <v>469.2</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>90.17</v>
+        <v>479.57</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>91.31</v>
+        <v>479.57</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>86.53</v>
+        <v>466.14</v>
       </c>
       <c r="H156" s="6" t="n">
         <v>2.21</v>
@@ -19115,30 +19115,30 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>96.36</v>
+        <v>586.86</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>597.24</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>99.12</v>
+        <v>598.97</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>95.41</v>
+        <v>584.4</v>
       </c>
       <c r="H174" s="6" t="n">
         <v>1.77</v>
@@ -19147,30 +19147,30 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>586.86</v>
+        <v>96.36</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>597.24</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>598.97</v>
+        <v>99.12</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>584.4</v>
+        <v>95.41</v>
       </c>
       <c r="H175" s="6" t="n">
         <v>1.77</v>
@@ -19339,30 +19339,30 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Broadridge Financial Solutions</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
-        <v>57.07</v>
+        <v>147.47</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>58.01</v>
+        <v>149.91</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>59.37</v>
+        <v>153.06</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>57.05</v>
+        <v>146.02</v>
       </c>
       <c r="H181" s="6" t="n">
         <v>1.65</v>
@@ -19371,30 +19371,30 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>147.47</v>
+        <v>57.07</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>149.91</v>
+        <v>58.01</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>153.06</v>
+        <v>59.37</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>146.02</v>
+        <v>57.05</v>
       </c>
       <c r="H182" s="6" t="n">
         <v>1.65</v>
@@ -19595,30 +19595,30 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
-        <v>157.52</v>
+        <v>303.44</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>159.84</v>
+        <v>307.9</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>161.77</v>
+        <v>307.99</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>156.58</v>
+        <v>296.57</v>
       </c>
       <c r="H189" s="6" t="n">
         <v>1.47</v>
@@ -19627,30 +19627,30 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>303.44</v>
+        <v>157.52</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>307.9</v>
+        <v>159.84</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>307.99</v>
+        <v>161.77</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>296.57</v>
+        <v>156.58</v>
       </c>
       <c r="H190" s="6" t="n">
         <v>1.47</v>
@@ -20011,12 +20011,12 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Ametek</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -20025,16 +20025,16 @@
         </is>
       </c>
       <c r="D202" s="5" t="n">
-        <v>121.22</v>
+        <v>233.98</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>122.78</v>
+        <v>237</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>125.3</v>
+        <v>237.3</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>121.21</v>
+        <v>232.1</v>
       </c>
       <c r="H202" s="6" t="n">
         <v>1.29</v>
@@ -20043,12 +20043,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Ametek</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -20057,16 +20057,16 @@
         </is>
       </c>
       <c r="D203" s="5" t="n">
-        <v>233.98</v>
+        <v>121.22</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>237</v>
+        <v>122.78</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>237.3</v>
+        <v>125.3</v>
       </c>
       <c r="G203" s="5" t="n">
-        <v>232.1</v>
+        <v>121.21</v>
       </c>
       <c r="H203" s="6" t="n">
         <v>1.29</v>
@@ -20395,30 +20395,30 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>PulteGroup</t>
+          <t>KeyCorp</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D214" s="5" t="n">
-        <v>124.75</v>
+        <v>23.3</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>126.08</v>
+        <v>23.55</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>129.02</v>
+        <v>23.99</v>
       </c>
       <c r="G214" s="5" t="n">
-        <v>123.75</v>
+        <v>23.22</v>
       </c>
       <c r="H214" s="6" t="n">
         <v>1.07</v>
@@ -20459,12 +20459,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>KeyCorp</t>
+          <t>Hartford (The)</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -20473,16 +20473,16 @@
         </is>
       </c>
       <c r="D216" s="5" t="n">
-        <v>23.3</v>
+        <v>138.78</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>23.55</v>
+        <v>140.26</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>23.99</v>
+        <v>140.78</v>
       </c>
       <c r="G216" s="5" t="n">
-        <v>23.22</v>
+        <v>134.5</v>
       </c>
       <c r="H216" s="6" t="n">
         <v>1.07</v>
@@ -20491,30 +20491,30 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Hartford (The)</t>
+          <t>PulteGroup</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
-        <v>138.78</v>
+        <v>124.75</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>140.26</v>
+        <v>126.08</v>
       </c>
       <c r="F217" s="5" t="n">
-        <v>140.78</v>
+        <v>129.02</v>
       </c>
       <c r="G217" s="5" t="n">
-        <v>134.5</v>
+        <v>123.75</v>
       </c>
       <c r="H217" s="6" t="n">
         <v>1.07</v>
@@ -20683,30 +20683,30 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>1055.18</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>1065.22</v>
+        <v>88.8</v>
       </c>
       <c r="F223" s="5" t="n">
-        <v>1152.07</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1045.91</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="H223" s="6" t="n">
         <v>0.95</v>
@@ -20715,30 +20715,30 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D224" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>1055.18</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>88.8</v>
+        <v>1065.22</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>1152.07</v>
       </c>
       <c r="G224" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>1045.91</v>
       </c>
       <c r="H224" s="6" t="n">
         <v>0.95</v>
@@ -21067,30 +21067,30 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
-        <v>92.23999999999999</v>
+        <v>363.39</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>92.98</v>
+        <v>366.29</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>94.06999999999999</v>
+        <v>371.58</v>
       </c>
       <c r="G235" s="5" t="n">
-        <v>91.03</v>
+        <v>355.25</v>
       </c>
       <c r="H235" s="6" t="n">
         <v>0.8</v>
@@ -21099,30 +21099,30 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D236" s="5" t="n">
-        <v>363.39</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>366.29</v>
+        <v>92.98</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>371.58</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="G236" s="5" t="n">
-        <v>355.25</v>
+        <v>91.03</v>
       </c>
       <c r="H236" s="6" t="n">
         <v>0.8</v>
@@ -21611,30 +21611,30 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D252" s="5" t="n">
-        <v>257.54</v>
+        <v>134.68</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>258.69</v>
+        <v>135.29</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>270.73</v>
+        <v>135.29</v>
       </c>
       <c r="G252" s="5" t="n">
-        <v>257.54</v>
+        <v>132.66</v>
       </c>
       <c r="H252" s="6" t="n">
         <v>0.45</v>
@@ -21643,30 +21643,30 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>EQR</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>Equity Residential</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>134.68</v>
+        <v>68.69</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>135.29</v>
+        <v>69</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>135.29</v>
+        <v>70</v>
       </c>
       <c r="G253" s="5" t="n">
-        <v>132.66</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="H253" s="6" t="n">
         <v>0.45</v>
@@ -21675,30 +21675,30 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D254" s="5" t="n">
-        <v>136.63</v>
+        <v>257.54</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>137.24</v>
+        <v>258.69</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>139.48</v>
+        <v>270.73</v>
       </c>
       <c r="G254" s="5" t="n">
-        <v>135.82</v>
+        <v>257.54</v>
       </c>
       <c r="H254" s="6" t="n">
         <v>0.45</v>
@@ -21707,30 +21707,30 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>EQR</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Equity Residential</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>68.69</v>
+        <v>136.63</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>69</v>
+        <v>137.24</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>70</v>
+        <v>139.48</v>
       </c>
       <c r="G255" s="5" t="n">
-        <v>68.26000000000001</v>
+        <v>135.82</v>
       </c>
       <c r="H255" s="6" t="n">
         <v>0.45</v>
@@ -21739,30 +21739,30 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>251.38</v>
+        <v>87.16</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>252.39</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>258.12</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>251.38</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H256" s="6" t="n">
         <v>0.4</v>
@@ -21771,30 +21771,30 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
-        <v>87.16</v>
+        <v>184.4</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>87.51000000000001</v>
+        <v>185.13</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>88.06999999999999</v>
+        <v>185.7</v>
       </c>
       <c r="G257" s="5" t="n">
-        <v>85.29000000000001</v>
+        <v>180.96</v>
       </c>
       <c r="H257" s="6" t="n">
         <v>0.4</v>
@@ -21803,30 +21803,30 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D258" s="5" t="n">
-        <v>184.4</v>
+        <v>251.38</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>185.13</v>
+        <v>252.39</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>185.7</v>
+        <v>258.12</v>
       </c>
       <c r="G258" s="5" t="n">
-        <v>180.96</v>
+        <v>251.38</v>
       </c>
       <c r="H258" s="6" t="n">
         <v>0.4</v>
@@ -21995,12 +21995,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Wabtec</t>
+          <t>Copart</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -22009,16 +22009,16 @@
         </is>
       </c>
       <c r="D264" s="5" t="n">
-        <v>261.21</v>
+        <v>27.52</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>262.08</v>
+        <v>27.61</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>263.89</v>
+        <v>28.29</v>
       </c>
       <c r="G264" s="5" t="n">
-        <v>259.71</v>
+        <v>27.28</v>
       </c>
       <c r="H264" s="6" t="n">
         <v>0.33</v>
@@ -22027,12 +22027,12 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Copart</t>
+          <t>Wabtec</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -22041,16 +22041,16 @@
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>27.52</v>
+        <v>261.21</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>27.61</v>
+        <v>262.08</v>
       </c>
       <c r="F265" s="5" t="n">
-        <v>28.29</v>
+        <v>263.89</v>
       </c>
       <c r="G265" s="5" t="n">
-        <v>27.28</v>
+        <v>259.71</v>
       </c>
       <c r="H265" s="6" t="n">
         <v>0.33</v>
@@ -22315,30 +22315,30 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D274" s="5" t="n">
-        <v>634.6</v>
+        <v>168.12</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>635.52</v>
+        <v>168.36</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>635.52</v>
+        <v>170.3</v>
       </c>
       <c r="G274" s="5" t="n">
-        <v>623.1</v>
+        <v>166.98</v>
       </c>
       <c r="H274" s="6" t="n">
         <v>0.14</v>
@@ -22347,30 +22347,30 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
-        <v>168.12</v>
+        <v>634.6</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>168.36</v>
+        <v>635.52</v>
       </c>
       <c r="F275" s="5" t="n">
-        <v>170.3</v>
+        <v>635.52</v>
       </c>
       <c r="G275" s="5" t="n">
-        <v>166.98</v>
+        <v>623.1</v>
       </c>
       <c r="H275" s="6" t="n">
         <v>0.14</v>
@@ -22699,30 +22699,30 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D286" s="5" t="n">
-        <v>52.82</v>
+        <v>160.71</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>52.72</v>
+        <v>160.41</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>53.75</v>
+        <v>163.06</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>51.58</v>
+        <v>156.79</v>
       </c>
       <c r="H286" s="7" t="n">
         <v>-0.19</v>
@@ -22731,30 +22731,30 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>Trimble Inc.</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
-        <v>160.71</v>
+        <v>52.82</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>160.41</v>
+        <v>52.72</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>163.06</v>
+        <v>53.75</v>
       </c>
       <c r="G287" s="5" t="n">
-        <v>156.79</v>
+        <v>51.58</v>
       </c>
       <c r="H287" s="7" t="n">
         <v>-0.19</v>
@@ -22923,30 +22923,30 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>O’Reilly Automotive</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>74.81999999999999</v>
+        <v>86.28</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>74.62</v>
+        <v>86.05</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>75.04000000000001</v>
+        <v>87.28</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>73.79000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="H293" s="7" t="n">
         <v>-0.27</v>
@@ -22955,30 +22955,30 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>O’Reilly Automotive</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>86.28</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>86.05</v>
+        <v>74.62</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>87.28</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="G294" s="5" t="n">
-        <v>82.73</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="H294" s="7" t="n">
         <v>-0.27</v>
@@ -23307,30 +23307,30 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
-        <v>274.31</v>
+        <v>314.69</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>272.83</v>
+        <v>312.98</v>
       </c>
       <c r="F305" s="5" t="n">
-        <v>275.71</v>
+        <v>318.2</v>
       </c>
       <c r="G305" s="5" t="n">
-        <v>269.75</v>
+        <v>312.98</v>
       </c>
       <c r="H305" s="7" t="n">
         <v>-0.54</v>
@@ -23339,30 +23339,30 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>314.69</v>
+        <v>274.31</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>312.98</v>
+        <v>272.83</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>318.2</v>
+        <v>275.71</v>
       </c>
       <c r="G306" s="5" t="n">
-        <v>312.98</v>
+        <v>269.75</v>
       </c>
       <c r="H306" s="7" t="n">
         <v>-0.54</v>
@@ -23467,30 +23467,30 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Genuine Parts Company</t>
+          <t>Estée Lauder Companies (The)</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D310" s="5" t="n">
-        <v>125.62</v>
+        <v>82.66</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>124.82</v>
+        <v>82.13</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>125.66</v>
+        <v>82.84</v>
       </c>
       <c r="G310" s="5" t="n">
-        <v>121</v>
+        <v>80.86</v>
       </c>
       <c r="H310" s="7" t="n">
         <v>-0.64</v>
@@ -23499,30 +23499,30 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Estée Lauder Companies (The)</t>
+          <t>Genuine Parts Company</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
-        <v>82.66</v>
+        <v>125.62</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>82.13</v>
+        <v>124.82</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>82.84</v>
+        <v>125.66</v>
       </c>
       <c r="G311" s="5" t="n">
-        <v>80.86</v>
+        <v>121</v>
       </c>
       <c r="H311" s="7" t="n">
         <v>-0.64</v>
@@ -23659,30 +23659,30 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Norwegian Cruise Line Holdings</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D316" s="5" t="n">
-        <v>207.85</v>
+        <v>19.61</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>206.26</v>
+        <v>19.46</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>210.49</v>
+        <v>19.73</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>206.26</v>
+        <v>19.46</v>
       </c>
       <c r="H316" s="7" t="n">
         <v>-0.76</v>
@@ -23691,30 +23691,30 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D317" s="5" t="n">
-        <v>19.61</v>
+        <v>207.85</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>19.46</v>
+        <v>206.26</v>
       </c>
       <c r="F317" s="5" t="n">
-        <v>19.73</v>
+        <v>210.49</v>
       </c>
       <c r="G317" s="5" t="n">
-        <v>19.46</v>
+        <v>206.26</v>
       </c>
       <c r="H317" s="7" t="n">
         <v>-0.76</v>
@@ -23787,30 +23787,30 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Lilly (Eli)</t>
+          <t>W. R. Berkley Corporation</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>1188.58</v>
+        <v>72.19</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>1179.11</v>
+        <v>71.61</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>1188.58</v>
+        <v>73.84</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>1152.54</v>
+        <v>69.88</v>
       </c>
       <c r="H320" s="7" t="n">
         <v>-0.8</v>
@@ -23819,30 +23819,30 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>83.87</v>
+        <v>333.99</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>83.2</v>
+        <v>331.32</v>
       </c>
       <c r="F321" s="5" t="n">
-        <v>83.87</v>
+        <v>338.14</v>
       </c>
       <c r="G321" s="5" t="n">
-        <v>79.3</v>
+        <v>328.5</v>
       </c>
       <c r="H321" s="7" t="n">
         <v>-0.8</v>
@@ -23851,30 +23851,30 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Lilly (Eli)</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D322" s="5" t="n">
-        <v>333.99</v>
+        <v>1188.58</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>331.32</v>
+        <v>1179.11</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>338.14</v>
+        <v>1188.58</v>
       </c>
       <c r="G322" s="5" t="n">
-        <v>328.5</v>
+        <v>1152.54</v>
       </c>
       <c r="H322" s="7" t="n">
         <v>-0.8</v>
@@ -23883,30 +23883,30 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D323" s="5" t="n">
-        <v>72.19</v>
+        <v>83.87</v>
       </c>
       <c r="E323" s="5" t="n">
-        <v>71.61</v>
+        <v>83.2</v>
       </c>
       <c r="F323" s="5" t="n">
-        <v>73.84</v>
+        <v>83.87</v>
       </c>
       <c r="G323" s="5" t="n">
-        <v>69.88</v>
+        <v>79.3</v>
       </c>
       <c r="H323" s="7" t="n">
         <v>-0.8</v>
@@ -24011,30 +24011,30 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Carrier Global</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>43.54</v>
+        <v>69.34</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>43.13</v>
+        <v>68.69</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>44.13</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="G327" s="5" t="n">
-        <v>42.72</v>
+        <v>68.61</v>
       </c>
       <c r="H327" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -24043,30 +24043,30 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>Carrier Global</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>69.34</v>
+        <v>43.54</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>68.69</v>
+        <v>43.13</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>69.76000000000001</v>
+        <v>44.13</v>
       </c>
       <c r="G328" s="5" t="n">
-        <v>68.61</v>
+        <v>42.72</v>
       </c>
       <c r="H328" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -24171,30 +24171,30 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D332" s="5" t="n">
-        <v>112.94</v>
+        <v>159.07</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>111.55</v>
+        <v>157.12</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>113.43</v>
+        <v>167.21</v>
       </c>
       <c r="G332" s="5" t="n">
-        <v>111.38</v>
+        <v>157.12</v>
       </c>
       <c r="H332" s="7" t="n">
         <v>-1.23</v>
@@ -24203,30 +24203,30 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>159.07</v>
+        <v>112.94</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>157.12</v>
+        <v>111.55</v>
       </c>
       <c r="F333" s="5" t="n">
-        <v>167.21</v>
+        <v>113.43</v>
       </c>
       <c r="G333" s="5" t="n">
-        <v>157.12</v>
+        <v>111.38</v>
       </c>
       <c r="H333" s="7" t="n">
         <v>-1.23</v>
@@ -24267,30 +24267,30 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Home Depot (The)</t>
+          <t>Hershey Company (The)</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>343.3</v>
+        <v>173.66</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>338.87</v>
+        <v>171.42</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>348.02</v>
+        <v>175.24</v>
       </c>
       <c r="G335" s="5" t="n">
-        <v>337.11</v>
+        <v>170.27</v>
       </c>
       <c r="H335" s="7" t="n">
         <v>-1.29</v>
@@ -24299,30 +24299,30 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Hershey Company (The)</t>
+          <t>Home Depot (The)</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>173.66</v>
+        <v>343.3</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>171.42</v>
+        <v>338.87</v>
       </c>
       <c r="F336" s="5" t="n">
-        <v>175.24</v>
+        <v>348.02</v>
       </c>
       <c r="G336" s="5" t="n">
-        <v>170.27</v>
+        <v>337.11</v>
       </c>
       <c r="H336" s="7" t="n">
         <v>-1.29</v>
@@ -24715,30 +24715,30 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>115.05</v>
+        <v>26.83</v>
       </c>
       <c r="E349" s="5" t="n">
-        <v>113.24</v>
+        <v>26.41</v>
       </c>
       <c r="F349" s="5" t="n">
-        <v>115.41</v>
+        <v>26.86</v>
       </c>
       <c r="G349" s="5" t="n">
-        <v>113.24</v>
+        <v>26.41</v>
       </c>
       <c r="H349" s="7" t="n">
         <v>-1.57</v>
@@ -24747,30 +24747,30 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D350" s="5" t="n">
-        <v>26.83</v>
+        <v>115.05</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>26.41</v>
+        <v>113.24</v>
       </c>
       <c r="F350" s="5" t="n">
-        <v>26.86</v>
+        <v>115.41</v>
       </c>
       <c r="G350" s="5" t="n">
-        <v>26.41</v>
+        <v>113.24</v>
       </c>
       <c r="H350" s="7" t="n">
         <v>-1.57</v>
@@ -24811,30 +24811,30 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D352" s="5" t="n">
-        <v>80.06</v>
+        <v>47.76</v>
       </c>
       <c r="E352" s="5" t="n">
-        <v>78.77</v>
+        <v>46.99</v>
       </c>
       <c r="F352" s="5" t="n">
-        <v>80.48</v>
+        <v>47.76</v>
       </c>
       <c r="G352" s="5" t="n">
-        <v>78.77</v>
+        <v>46.99</v>
       </c>
       <c r="H352" s="7" t="n">
         <v>-1.61</v>
@@ -24843,30 +24843,30 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>47.76</v>
+        <v>80.06</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>46.99</v>
+        <v>78.77</v>
       </c>
       <c r="F353" s="5" t="n">
-        <v>47.76</v>
+        <v>80.48</v>
       </c>
       <c r="G353" s="5" t="n">
-        <v>46.99</v>
+        <v>78.77</v>
       </c>
       <c r="H353" s="7" t="n">
         <v>-1.61</v>
@@ -25995,30 +25995,30 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class C)</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>355.03</v>
+        <v>274.6</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>346.12</v>
+        <v>267.71</v>
       </c>
       <c r="F389" s="5" t="n">
-        <v>370.21</v>
+        <v>274.6</v>
       </c>
       <c r="G389" s="5" t="n">
-        <v>346.12</v>
+        <v>264.95</v>
       </c>
       <c r="H389" s="7" t="n">
         <v>-2.51</v>
@@ -26027,30 +26027,30 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D390" s="5" t="n">
-        <v>274.6</v>
+        <v>355.03</v>
       </c>
       <c r="E390" s="5" t="n">
-        <v>267.71</v>
+        <v>346.12</v>
       </c>
       <c r="F390" s="5" t="n">
-        <v>274.6</v>
+        <v>370.21</v>
       </c>
       <c r="G390" s="5" t="n">
-        <v>264.95</v>
+        <v>346.12</v>
       </c>
       <c r="H390" s="7" t="n">
         <v>-2.51</v>
@@ -26539,30 +26539,30 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>359.27</v>
+        <v>357.18</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>348.83</v>
+        <v>346.77</v>
       </c>
       <c r="F406" s="5" t="n">
-        <v>360.35</v>
+        <v>370.92</v>
       </c>
       <c r="G406" s="5" t="n">
-        <v>345.73</v>
+        <v>346.77</v>
       </c>
       <c r="H406" s="7" t="n">
         <v>-2.91</v>
@@ -26571,30 +26571,30 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>357.18</v>
+        <v>359.27</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>346.77</v>
+        <v>348.83</v>
       </c>
       <c r="F407" s="5" t="n">
-        <v>370.92</v>
+        <v>360.35</v>
       </c>
       <c r="G407" s="5" t="n">
-        <v>346.77</v>
+        <v>345.73</v>
       </c>
       <c r="H407" s="7" t="n">
         <v>-2.91</v>
@@ -26667,30 +26667,30 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D410" s="5" t="n">
-        <v>1352.74</v>
+        <v>329.78</v>
       </c>
       <c r="E410" s="5" t="n">
-        <v>1312</v>
+        <v>319.87</v>
       </c>
       <c r="F410" s="5" t="n">
-        <v>1376.41</v>
+        <v>331.45</v>
       </c>
       <c r="G410" s="5" t="n">
-        <v>1291.38</v>
+        <v>311.07</v>
       </c>
       <c r="H410" s="7" t="n">
         <v>-3.01</v>
@@ -26731,30 +26731,30 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Monolithic Power Systems</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D412" s="5" t="n">
-        <v>329.78</v>
+        <v>1352.74</v>
       </c>
       <c r="E412" s="5" t="n">
-        <v>319.87</v>
+        <v>1312</v>
       </c>
       <c r="F412" s="5" t="n">
-        <v>331.45</v>
+        <v>1376.41</v>
       </c>
       <c r="G412" s="5" t="n">
-        <v>311.07</v>
+        <v>1291.38</v>
       </c>
       <c r="H412" s="7" t="n">
         <v>-3.01</v>
@@ -27356,7 +27356,7 @@
         <v>220.75</v>
       </c>
       <c r="E431" s="5" t="n">
-        <v>211.62</v>
+        <v>211.63</v>
       </c>
       <c r="F431" s="5" t="n">
         <v>220.75</v>
@@ -28220,13 +28220,13 @@
         <v>399.97</v>
       </c>
       <c r="E458" s="5" t="n">
-        <v>370.82</v>
+        <v>370.83</v>
       </c>
       <c r="F458" s="5" t="n">
         <v>399.97</v>
       </c>
       <c r="G458" s="5" t="n">
-        <v>370.82</v>
+        <v>370.83</v>
       </c>
       <c r="H458" s="7" t="n">
         <v>-7.29</v>
@@ -28267,12 +28267,12 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="C460" s="4" t="inlineStr">
@@ -28281,16 +28281,16 @@
         </is>
       </c>
       <c r="D460" s="5" t="n">
-        <v>121.31</v>
+        <v>144.39</v>
       </c>
       <c r="E460" s="5" t="n">
-        <v>111.94</v>
+        <v>133.24</v>
       </c>
       <c r="F460" s="5" t="n">
-        <v>121.31</v>
+        <v>144.39</v>
       </c>
       <c r="G460" s="5" t="n">
-        <v>109.66</v>
+        <v>130.86</v>
       </c>
       <c r="H460" s="7" t="n">
         <v>-7.72</v>
@@ -28299,12 +28299,12 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C461" s="4" t="inlineStr">
@@ -28313,16 +28313,16 @@
         </is>
       </c>
       <c r="D461" s="5" t="n">
-        <v>144.39</v>
+        <v>121.31</v>
       </c>
       <c r="E461" s="5" t="n">
-        <v>133.24</v>
+        <v>111.94</v>
       </c>
       <c r="F461" s="5" t="n">
-        <v>144.39</v>
+        <v>121.31</v>
       </c>
       <c r="G461" s="5" t="n">
-        <v>130.86</v>
+        <v>109.66</v>
       </c>
       <c r="H461" s="7" t="n">
         <v>-7.72</v>
@@ -28907,30 +28907,30 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D480" s="5" t="n">
-        <v>186.96</v>
+        <v>565.8</v>
       </c>
       <c r="E480" s="5" t="n">
-        <v>168.61</v>
+        <v>510.28</v>
       </c>
       <c r="F480" s="5" t="n">
-        <v>186.96</v>
+        <v>565.8</v>
       </c>
       <c r="G480" s="5" t="n">
-        <v>168.56</v>
+        <v>510.28</v>
       </c>
       <c r="H480" s="7" t="n">
         <v>-9.81</v>
@@ -28939,30 +28939,30 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D481" s="5" t="n">
-        <v>565.8</v>
+        <v>186.96</v>
       </c>
       <c r="E481" s="5" t="n">
-        <v>510.28</v>
+        <v>168.61</v>
       </c>
       <c r="F481" s="5" t="n">
-        <v>565.8</v>
+        <v>186.96</v>
       </c>
       <c r="G481" s="5" t="n">
-        <v>510.28</v>
+        <v>168.56</v>
       </c>
       <c r="H481" s="7" t="n">
         <v>-9.81</v>
@@ -29372,13 +29372,13 @@
         <v>445.5</v>
       </c>
       <c r="E494" s="5" t="n">
-        <v>384.27</v>
+        <v>384.28</v>
       </c>
       <c r="F494" s="5" t="n">
         <v>445.5</v>
       </c>
       <c r="G494" s="5" t="n">
-        <v>384.27</v>
+        <v>384.28</v>
       </c>
       <c r="H494" s="7" t="n">
         <v>-13.74</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Jul 16-&gt;Jul 17) and rolling 5-day  |  updated 2026-07-18 03:56</t>
+          <t>Daily (Jul 16-&gt;Jul 17) and rolling 5-day  |  updated 2026-07-19 04:06</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 16 close to Jul 17 close  |  503 companies  |  updated 2026-07-19 04:06</t>
+          <t>Jul 16 close to Jul 17 close  |  503 companies  |  updated 2026-07-20 04:12</t>
         </is>
       </c>
     </row>
@@ -2025,24 +2025,24 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>316.23</v>
+        <v>110.91</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>319.51</v>
+        <v>112.06</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>1.04</v>
@@ -2051,24 +2051,24 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>110.91</v>
+        <v>205.8</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>112.06</v>
+        <v>207.95</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>1.04</v>
@@ -2077,24 +2077,24 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>205.8</v>
+        <v>316.23</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>207.95</v>
+        <v>319.51</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>1.04</v>
@@ -2181,24 +2181,24 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Eaton Corporation</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>280.27</v>
+        <v>396.27</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>282.91</v>
+        <v>399.99</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -2207,24 +2207,24 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>396.27</v>
+        <v>280.27</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>399.99</v>
+        <v>282.91</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -2311,12 +2311,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>265.04</v>
+        <v>275.22</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>267.4</v>
+        <v>277.66</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>0.89</v>
@@ -2337,12 +2337,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>275.22</v>
+        <v>265.04</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>277.66</v>
+        <v>267.4</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>0.89</v>
@@ -2519,24 +2519,24 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>630.86</v>
+        <v>134.29</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>635.52</v>
+        <v>135.29</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>0.74</v>
@@ -2545,24 +2545,24 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>134.29</v>
+        <v>630.86</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>135.29</v>
+        <v>635.52</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>0.74</v>
@@ -2935,24 +2935,24 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Oneok</t>
+          <t>Crown Castle</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>93</v>
+        <v>78.73</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>93.52</v>
+        <v>79.17</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>0.5600000000000001</v>
@@ -2961,24 +2961,24 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Crown Castle</t>
+          <t>Oneok</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>78.73</v>
+        <v>93</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>79.17</v>
+        <v>93.52</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>0.5600000000000001</v>
@@ -3039,24 +3039,24 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Incyte</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>275.44</v>
+        <v>116.65</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>276.84</v>
+        <v>117.25</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>0.51</v>
@@ -3065,24 +3065,24 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>207.84</v>
+        <v>35.04</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>208.9</v>
+        <v>35.22</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>0.51</v>
@@ -3091,24 +3091,24 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>35.04</v>
+        <v>207.84</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>35.22</v>
+        <v>208.9</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>0.51</v>
@@ -3117,24 +3117,24 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Incyte</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>116.65</v>
+        <v>275.44</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>117.25</v>
+        <v>276.84</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>0.51</v>
@@ -3143,24 +3143,24 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>91.54000000000001</v>
+        <v>281.94</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>92</v>
+        <v>283.36</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>0.5</v>
@@ -3169,24 +3169,24 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>281.94</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>283.36</v>
+        <v>92</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>0.5</v>
@@ -3299,12 +3299,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Expeditors International</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>181.96</v>
+        <v>271.19</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>182.8</v>
+        <v>272.43</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>0.46</v>
@@ -3351,12 +3351,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Expeditors International</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>271.19</v>
+        <v>181.96</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>272.43</v>
+        <v>182.8</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>0.46</v>
@@ -3455,24 +3455,24 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>82.38</v>
+        <v>58.61</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>82.68000000000001</v>
+        <v>58.82</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>0.36</v>
@@ -3481,24 +3481,24 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>58.61</v>
+        <v>82.38</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>58.82</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>0.36</v>
@@ -3507,24 +3507,24 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>877.17</v>
+        <v>185.04</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>880.28</v>
+        <v>185.69</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>0.35</v>
@@ -3559,24 +3559,24 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>185.04</v>
+        <v>877.17</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>185.69</v>
+        <v>880.28</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>0.35</v>
@@ -3819,24 +3819,24 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Ares Management</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>125.43</v>
+        <v>188.3</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>125.68</v>
+        <v>188.68</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>0.2</v>
@@ -3845,24 +3845,24 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Ares Management</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>188.3</v>
+        <v>125.43</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>188.68</v>
+        <v>125.68</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>0.2</v>
@@ -3897,12 +3897,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>24.45</v>
+        <v>173.6</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>24.49</v>
+        <v>173.88</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>0.16</v>
@@ -3923,12 +3923,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>173.6</v>
+        <v>24.45</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>173.88</v>
+        <v>24.49</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0.16</v>
@@ -4001,24 +4001,24 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>333.26</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>333.74</v>
+        <v>85.41</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>0.14</v>
@@ -4027,24 +4027,24 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>85.29000000000001</v>
+        <v>333.26</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>85.41</v>
+        <v>333.74</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>0.14</v>
@@ -4183,12 +4183,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>211.93</v>
+        <v>168.56</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>211.99</v>
+        <v>168.61</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>0.03</v>
@@ -4209,12 +4209,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>168.56</v>
+        <v>211.93</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>168.61</v>
+        <v>211.99</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>0.03</v>
@@ -4235,24 +4235,24 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Marsh McLennan</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
-        <v>182.15</v>
+        <v>322.3</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>182.18</v>
+        <v>322.36</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>0.02</v>
@@ -4261,24 +4261,24 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Marsh McLennan</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
-        <v>322.3</v>
+        <v>182.15</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>322.36</v>
+        <v>182.18</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>0.02</v>
@@ -4287,24 +4287,24 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>228.38</v>
+        <v>841.3099999999999</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>228.41</v>
+        <v>841.39</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>0.01</v>
@@ -4313,24 +4313,24 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Williams-Sonoma, Inc.</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>841.3099999999999</v>
+        <v>228.38</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>841.39</v>
+        <v>228.41</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>0.01</v>
@@ -4391,24 +4391,24 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Expand Energy</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>65.75</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>65.70999999999999</v>
+        <v>88.13</v>
       </c>
       <c r="F153" s="7" t="n">
         <v>-0.06</v>
@@ -4417,24 +4417,24 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Expand Energy</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>88.18000000000001</v>
+        <v>65.75</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>88.13</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F154" s="7" t="n">
         <v>-0.06</v>
@@ -4833,24 +4833,24 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Kenvue</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>154.79</v>
+        <v>19.02</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>154.46</v>
+        <v>18.98</v>
       </c>
       <c r="F170" s="7" t="n">
         <v>-0.21</v>
@@ -4859,24 +4859,24 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Kenvue</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>19.02</v>
+        <v>154.79</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>18.98</v>
+        <v>154.46</v>
       </c>
       <c r="F171" s="7" t="n">
         <v>-0.21</v>
@@ -4937,24 +4937,24 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Insulet Corporation</t>
+          <t>O’Reilly Automotive</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>164.43</v>
+        <v>86.25</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>164.06</v>
+        <v>86.05</v>
       </c>
       <c r="F174" s="7" t="n">
         <v>-0.23</v>
@@ -4963,24 +4963,24 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>O’Reilly Automotive</t>
+          <t>Insulet Corporation</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>86.25</v>
+        <v>164.43</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>86.05</v>
+        <v>164.06</v>
       </c>
       <c r="F175" s="7" t="n">
         <v>-0.23</v>
@@ -5145,24 +5145,24 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>58.56</v>
+        <v>294.33</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>58.38</v>
+        <v>293.43</v>
       </c>
       <c r="F182" s="7" t="n">
         <v>-0.31</v>
@@ -5171,24 +5171,24 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>294.33</v>
+        <v>58.56</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>293.43</v>
+        <v>58.38</v>
       </c>
       <c r="F183" s="7" t="n">
         <v>-0.31</v>
@@ -5197,24 +5197,24 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D184" s="5" t="n">
-        <v>678.9400000000001</v>
+        <v>203.76</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>676.6900000000001</v>
+        <v>203.08</v>
       </c>
       <c r="F184" s="7" t="n">
         <v>-0.33</v>
@@ -5223,24 +5223,24 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Regeneron Pharmaceuticals</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>203.76</v>
+        <v>678.9400000000001</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>203.08</v>
+        <v>676.6900000000001</v>
       </c>
       <c r="F185" s="7" t="n">
         <v>-0.33</v>
@@ -5249,24 +5249,24 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D186" s="5" t="n">
-        <v>25.14</v>
+        <v>61.49</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>25.05</v>
+        <v>61.27</v>
       </c>
       <c r="F186" s="7" t="n">
         <v>-0.36</v>
@@ -5275,24 +5275,24 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
-        <v>61.49</v>
+        <v>25.14</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>61.27</v>
+        <v>25.05</v>
       </c>
       <c r="F187" s="7" t="n">
         <v>-0.36</v>
@@ -5353,12 +5353,12 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>Comfort Systems USA</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>631.02</v>
+        <v>1680.6</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>628.53</v>
+        <v>1674.06</v>
       </c>
       <c r="F190" s="7" t="n">
         <v>-0.39</v>
@@ -5379,24 +5379,24 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Aon plc</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
-        <v>368.63</v>
+        <v>631.02</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>367.21</v>
+        <v>628.53</v>
       </c>
       <c r="F191" s="7" t="n">
         <v>-0.39</v>
@@ -5405,24 +5405,24 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Comfort Systems USA</t>
+          <t>Aon plc</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>1680.6</v>
+        <v>368.63</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1674.06</v>
+        <v>367.21</v>
       </c>
       <c r="F192" s="7" t="n">
         <v>-0.39</v>
@@ -5691,12 +5691,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>DTE Energy</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="D203" s="5" t="n">
-        <v>148.91</v>
+        <v>43.34</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>148.19</v>
+        <v>43.13</v>
       </c>
       <c r="F203" s="7" t="n">
         <v>-0.48</v>
@@ -5717,12 +5717,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>DTE Energy</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>43.34</v>
+        <v>148.91</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>43.13</v>
+        <v>148.19</v>
       </c>
       <c r="F204" s="7" t="n">
         <v>-0.48</v>
@@ -5795,24 +5795,24 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>246.27</v>
+        <v>256.56</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>245.05</v>
+        <v>255.27</v>
       </c>
       <c r="F207" s="7" t="n">
         <v>-0.5</v>
@@ -5821,24 +5821,24 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>945.5700000000001</v>
+        <v>246.27</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>940.87</v>
+        <v>245.05</v>
       </c>
       <c r="F208" s="7" t="n">
         <v>-0.5</v>
@@ -5847,24 +5847,24 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Henry Schein</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>853.2</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>848.95</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="F209" s="7" t="n">
         <v>-0.5</v>
@@ -5873,24 +5873,24 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Henry Schein</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D210" s="5" t="n">
-        <v>88.26000000000001</v>
+        <v>945.5700000000001</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>87.81999999999999</v>
+        <v>940.87</v>
       </c>
       <c r="F210" s="7" t="n">
         <v>-0.5</v>
@@ -5899,24 +5899,24 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>256.56</v>
+        <v>853.2</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>255.27</v>
+        <v>848.95</v>
       </c>
       <c r="F211" s="7" t="n">
         <v>-0.5</v>
@@ -5951,24 +5951,24 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Parker Hannifin</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
-        <v>78.05</v>
+        <v>958.34</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>77.63</v>
+        <v>953.21</v>
       </c>
       <c r="F213" s="7" t="n">
         <v>-0.54</v>
@@ -5977,24 +5977,24 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Parker Hannifin</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D214" s="5" t="n">
-        <v>958.34</v>
+        <v>78.05</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>953.21</v>
+        <v>77.63</v>
       </c>
       <c r="F214" s="7" t="n">
         <v>-0.54</v>
@@ -6003,24 +6003,24 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Air Products</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
-        <v>297.29</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>295.62</v>
+        <v>74.62</v>
       </c>
       <c r="F215" s="7" t="n">
         <v>-0.5600000000000001</v>
@@ -6029,24 +6029,24 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>Air Products</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D216" s="5" t="n">
-        <v>75.04000000000001</v>
+        <v>297.29</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>74.62</v>
+        <v>295.62</v>
       </c>
       <c r="F216" s="7" t="n">
         <v>-0.5600000000000001</v>
@@ -6055,24 +6055,24 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
-        <v>141.26</v>
+        <v>250.99</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>140.46</v>
+        <v>249.56</v>
       </c>
       <c r="F217" s="7" t="n">
         <v>-0.57</v>
@@ -6081,24 +6081,24 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D218" s="5" t="n">
-        <v>250.99</v>
+        <v>141.26</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>249.56</v>
+        <v>140.46</v>
       </c>
       <c r="F218" s="7" t="n">
         <v>-0.57</v>
@@ -6107,24 +6107,24 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Honeywell Technologies</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>205.01</v>
+        <v>226.33</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>203.83</v>
+        <v>225.02</v>
       </c>
       <c r="F219" s="7" t="n">
         <v>-0.58</v>
@@ -6159,24 +6159,24 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Technologies</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>226.33</v>
+        <v>205.01</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>225.02</v>
+        <v>203.83</v>
       </c>
       <c r="F221" s="7" t="n">
         <v>-0.58</v>
@@ -6237,24 +6237,24 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D224" s="5" t="n">
-        <v>89.34999999999999</v>
+        <v>114.95</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>88.8</v>
+        <v>114.24</v>
       </c>
       <c r="F224" s="7" t="n">
         <v>-0.62</v>
@@ -6263,24 +6263,24 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
-        <v>114.95</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>114.24</v>
+        <v>88.8</v>
       </c>
       <c r="F225" s="7" t="n">
         <v>-0.62</v>
@@ -6341,24 +6341,24 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Hasbro</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D228" s="5" t="n">
-        <v>43.88</v>
+        <v>82.09</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>43.59</v>
+        <v>81.55</v>
       </c>
       <c r="F228" s="7" t="n">
         <v>-0.66</v>
@@ -6367,24 +6367,24 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Hasbro</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
-        <v>82.09</v>
+        <v>43.88</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>81.55</v>
+        <v>43.59</v>
       </c>
       <c r="F229" s="7" t="n">
         <v>-0.66</v>
@@ -6575,24 +6575,24 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Kinder Morgan</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
-        <v>32.54</v>
+        <v>45.7</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>32.3</v>
+        <v>45.36</v>
       </c>
       <c r="F237" s="7" t="n">
         <v>-0.74</v>
@@ -6601,24 +6601,24 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Kinder Morgan</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D238" s="5" t="n">
-        <v>133.13</v>
+        <v>32.54</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>132.14</v>
+        <v>32.3</v>
       </c>
       <c r="F238" s="7" t="n">
         <v>-0.74</v>
@@ -6653,24 +6653,24 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>45.7</v>
+        <v>133.13</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>45.36</v>
+        <v>132.14</v>
       </c>
       <c r="F240" s="7" t="n">
         <v>-0.74</v>
@@ -6705,24 +6705,24 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D242" s="5" t="n">
-        <v>45.46</v>
+        <v>21.98</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>45.11</v>
+        <v>21.81</v>
       </c>
       <c r="F242" s="7" t="n">
         <v>-0.77</v>
@@ -6731,24 +6731,24 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
-        <v>21.98</v>
+        <v>45.46</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>21.81</v>
+        <v>45.11</v>
       </c>
       <c r="F243" s="7" t="n">
         <v>-0.77</v>
@@ -6783,12 +6783,12 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>255.93</v>
+        <v>169.7</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>253.9</v>
+        <v>168.36</v>
       </c>
       <c r="F245" s="7" t="n">
         <v>-0.79</v>
@@ -6809,12 +6809,12 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>169.7</v>
+        <v>255.93</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>168.36</v>
+        <v>253.9</v>
       </c>
       <c r="F246" s="7" t="n">
         <v>-0.79</v>
@@ -7043,24 +7043,24 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>126.11</v>
+        <v>206.25</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>125.01</v>
+        <v>204.45</v>
       </c>
       <c r="F255" s="7" t="n">
         <v>-0.87</v>
@@ -7069,24 +7069,24 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>206.25</v>
+        <v>126.11</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>204.45</v>
+        <v>125.01</v>
       </c>
       <c r="F256" s="7" t="n">
         <v>-0.87</v>
@@ -7147,24 +7147,24 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>News Corp (Class A)</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>28.69</v>
+        <v>71.69</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>28.43</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="F259" s="7" t="n">
         <v>-0.91</v>
@@ -7173,24 +7173,24 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>News Corp (Class A)</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D260" s="5" t="n">
-        <v>71.69</v>
+        <v>28.69</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>71.04000000000001</v>
+        <v>28.43</v>
       </c>
       <c r="F260" s="7" t="n">
         <v>-0.91</v>
@@ -7199,24 +7199,24 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>513.52</v>
+        <v>255.2</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>508.77</v>
+        <v>252.86</v>
       </c>
       <c r="F261" s="7" t="n">
         <v>-0.92</v>
@@ -7225,24 +7225,24 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D262" s="5" t="n">
-        <v>255.2</v>
+        <v>513.52</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>252.86</v>
+        <v>508.77</v>
       </c>
       <c r="F262" s="7" t="n">
         <v>-0.92</v>
@@ -7329,24 +7329,24 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D266" s="5" t="n">
-        <v>93.15000000000001</v>
+        <v>374.45</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>92.25</v>
+        <v>370.83</v>
       </c>
       <c r="F266" s="7" t="n">
         <v>-0.97</v>
@@ -7355,24 +7355,24 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
-        <v>374.45</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>370.83</v>
+        <v>92.25</v>
       </c>
       <c r="F267" s="7" t="n">
         <v>-0.97</v>
@@ -7459,24 +7459,24 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Gen Digital</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.01</v>
+        <v>533.21</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>26.74</v>
+        <v>527.87</v>
       </c>
       <c r="F271" s="7" t="n">
         <v>-1</v>
@@ -7485,24 +7485,24 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>151.5</v>
+        <v>114.49</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>149.98</v>
+        <v>113.35</v>
       </c>
       <c r="F272" s="7" t="n">
         <v>-1</v>
@@ -7511,24 +7511,24 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>114.49</v>
+        <v>151.5</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>113.35</v>
+        <v>149.98</v>
       </c>
       <c r="F273" s="7" t="n">
         <v>-1</v>
@@ -7537,24 +7537,24 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Gen Digital</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D274" s="5" t="n">
-        <v>533.21</v>
+        <v>27.01</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>527.87</v>
+        <v>26.74</v>
       </c>
       <c r="F274" s="7" t="n">
         <v>-1</v>
@@ -7589,24 +7589,24 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Vici Properties</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D276" s="5" t="n">
-        <v>27.15</v>
+        <v>500.94</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>26.87</v>
+        <v>495.76</v>
       </c>
       <c r="F276" s="7" t="n">
         <v>-1.03</v>
@@ -7615,24 +7615,24 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Vici Properties</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>500.94</v>
+        <v>27.15</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>495.76</v>
+        <v>26.87</v>
       </c>
       <c r="F277" s="7" t="n">
         <v>-1.03</v>
@@ -7719,24 +7719,24 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
-        <v>249.89</v>
+        <v>99.12</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>247.23</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F281" s="7" t="n">
         <v>-1.06</v>
@@ -7771,24 +7771,24 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>99.12</v>
+        <v>249.89</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>247.23</v>
       </c>
       <c r="F283" s="7" t="n">
         <v>-1.06</v>
@@ -7875,24 +7875,24 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
-        <v>127.16</v>
+        <v>118.68</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>125.75</v>
+        <v>117.36</v>
       </c>
       <c r="F287" s="7" t="n">
         <v>-1.11</v>
@@ -7901,24 +7901,24 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D288" s="5" t="n">
-        <v>118.68</v>
+        <v>127.16</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>117.36</v>
+        <v>125.75</v>
       </c>
       <c r="F288" s="7" t="n">
         <v>-1.11</v>
@@ -7979,24 +7979,24 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>46.79</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>46.26</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="F291" s="7" t="n">
         <v>-1.13</v>
@@ -8005,24 +8005,24 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D292" s="5" t="n">
-        <v>70.65000000000001</v>
+        <v>46.79</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>69.84999999999999</v>
+        <v>46.26</v>
       </c>
       <c r="F292" s="7" t="n">
         <v>-1.13</v>
@@ -8031,24 +8031,24 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>362.44</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>358.24</v>
+        <v>92.98</v>
       </c>
       <c r="F293" s="7" t="n">
         <v>-1.16</v>
@@ -8057,24 +8057,24 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>94.06999999999999</v>
+        <v>362.44</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>92.98</v>
+        <v>358.24</v>
       </c>
       <c r="F294" s="7" t="n">
         <v>-1.16</v>
@@ -8265,24 +8265,24 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>147.8</v>
+        <v>75.75</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>145.98</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="F302" s="7" t="n">
         <v>-1.23</v>
@@ -8291,24 +8291,24 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
-        <v>75.75</v>
+        <v>147.8</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>74.81999999999999</v>
+        <v>145.98</v>
       </c>
       <c r="F303" s="7" t="n">
         <v>-1.23</v>
@@ -8317,24 +8317,24 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Hormel Foods</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D304" s="5" t="n">
-        <v>90.83</v>
+        <v>25.71</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>89.7</v>
+        <v>25.39</v>
       </c>
       <c r="F304" s="7" t="n">
         <v>-1.24</v>
@@ -8343,24 +8343,24 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Hormel Foods</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
-        <v>25.71</v>
+        <v>90.83</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>25.39</v>
+        <v>89.7</v>
       </c>
       <c r="F305" s="7" t="n">
         <v>-1.24</v>
@@ -8577,24 +8577,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Kraft Heinz</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>201.21</v>
+        <v>26.23</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>198.53</v>
+        <v>25.88</v>
       </c>
       <c r="F314" s="7" t="n">
         <v>-1.33</v>
@@ -8603,24 +8603,24 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Kraft Heinz</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
-        <v>26.23</v>
+        <v>201.21</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>25.88</v>
+        <v>198.53</v>
       </c>
       <c r="F315" s="7" t="n">
         <v>-1.33</v>
@@ -8733,24 +8733,24 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>113.1</v>
+        <v>1087.05</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>111.55</v>
+        <v>1072.2</v>
       </c>
       <c r="F320" s="7" t="n">
         <v>-1.37</v>
@@ -8759,24 +8759,24 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>1087.05</v>
+        <v>113.1</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>1072.2</v>
+        <v>111.55</v>
       </c>
       <c r="F321" s="7" t="n">
         <v>-1.37</v>
@@ -8863,24 +8863,24 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D325" s="5" t="n">
-        <v>114.57</v>
+        <v>237.15</v>
       </c>
       <c r="E325" s="5" t="n">
-        <v>112.97</v>
+        <v>233.84</v>
       </c>
       <c r="F325" s="7" t="n">
         <v>-1.4</v>
@@ -8889,24 +8889,24 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D326" s="5" t="n">
-        <v>237.15</v>
+        <v>114.57</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>233.84</v>
+        <v>112.97</v>
       </c>
       <c r="F326" s="7" t="n">
         <v>-1.4</v>
@@ -8915,24 +8915,24 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>179.62</v>
+        <v>134.86</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>177.08</v>
+        <v>132.96</v>
       </c>
       <c r="F327" s="7" t="n">
         <v>-1.41</v>
@@ -8941,24 +8941,24 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>153.84</v>
+        <v>179.62</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>151.67</v>
+        <v>177.08</v>
       </c>
       <c r="F328" s="7" t="n">
         <v>-1.41</v>
@@ -8967,24 +8967,24 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>134.86</v>
+        <v>153.84</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>132.96</v>
+        <v>151.67</v>
       </c>
       <c r="F329" s="7" t="n">
         <v>-1.41</v>
@@ -9071,24 +9071,24 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Pinnacle West Capital</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>109.29</v>
+        <v>457.38</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>107.73</v>
+        <v>450.84</v>
       </c>
       <c r="F333" s="7" t="n">
         <v>-1.43</v>
@@ -9123,24 +9123,24 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PNW</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Pinnacle West Capital</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>457.38</v>
+        <v>109.29</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>450.84</v>
+        <v>107.73</v>
       </c>
       <c r="F335" s="7" t="n">
         <v>-1.43</v>
@@ -9149,24 +9149,24 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>551.54</v>
+        <v>520.74</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>543.6</v>
+        <v>513.22</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>-1.44</v>
@@ -9175,24 +9175,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D337" s="5" t="n">
-        <v>520.74</v>
+        <v>551.54</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>513.22</v>
+        <v>543.6</v>
       </c>
       <c r="F337" s="7" t="n">
         <v>-1.44</v>
@@ -9253,24 +9253,24 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>BF.B</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>Brown–Forman</t>
+          <t>PPL Corporation</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D340" s="5" t="n">
-        <v>25.96</v>
+        <v>36.38</v>
       </c>
       <c r="E340" s="5" t="n">
-        <v>25.58</v>
+        <v>35.85</v>
       </c>
       <c r="F340" s="7" t="n">
         <v>-1.46</v>
@@ -9279,24 +9279,24 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>BF.B</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>PPL Corporation</t>
+          <t>Brown–Forman</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>36.38</v>
+        <v>25.96</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>35.85</v>
+        <v>25.58</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>-1.46</v>
@@ -9435,24 +9435,24 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>31.38</v>
+        <v>98.11</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>30.91</v>
+        <v>96.64</v>
       </c>
       <c r="F347" s="7" t="n">
         <v>-1.5</v>
@@ -9461,24 +9461,24 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D348" s="5" t="n">
-        <v>98.11</v>
+        <v>31.38</v>
       </c>
       <c r="E348" s="5" t="n">
-        <v>96.64</v>
+        <v>30.91</v>
       </c>
       <c r="F348" s="7" t="n">
         <v>-1.5</v>
@@ -9513,24 +9513,24 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>Essex Property Trust</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D350" s="5" t="n">
-        <v>297.42</v>
+        <v>79.98</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>292.93</v>
+        <v>78.77</v>
       </c>
       <c r="F350" s="7" t="n">
         <v>-1.51</v>
@@ -9539,24 +9539,24 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Essex Property Trust</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>79.98</v>
+        <v>297.42</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>78.77</v>
+        <v>292.93</v>
       </c>
       <c r="F351" s="7" t="n">
         <v>-1.51</v>
@@ -9617,24 +9617,24 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>Palantir Technologies</t>
+          <t>Dover Corporation</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D354" s="5" t="n">
-        <v>134.44</v>
+        <v>217.51</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>132.38</v>
+        <v>214.18</v>
       </c>
       <c r="F354" s="7" t="n">
         <v>-1.53</v>
@@ -9643,24 +9643,24 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Dover Corporation</t>
+          <t>Palantir Technologies</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>217.51</v>
+        <v>134.44</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>214.18</v>
+        <v>132.38</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>-1.53</v>
@@ -9669,24 +9669,24 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D356" s="5" t="n">
-        <v>27.29</v>
+        <v>121.12</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>26.87</v>
+        <v>119.25</v>
       </c>
       <c r="F356" s="7" t="n">
         <v>-1.54</v>
@@ -9695,24 +9695,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>121.12</v>
+        <v>27.29</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>119.25</v>
+        <v>26.87</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>-1.54</v>
@@ -9851,24 +9851,24 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>277.89</v>
+        <v>139.48</v>
       </c>
       <c r="E363" s="5" t="n">
-        <v>273.41</v>
+        <v>137.24</v>
       </c>
       <c r="F363" s="7" t="n">
         <v>-1.61</v>
@@ -9877,24 +9877,24 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D364" s="5" t="n">
-        <v>31.01</v>
+        <v>277.89</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>30.51</v>
+        <v>273.41</v>
       </c>
       <c r="F364" s="7" t="n">
         <v>-1.61</v>
@@ -9903,24 +9903,24 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D365" s="5" t="n">
-        <v>139.48</v>
+        <v>31.01</v>
       </c>
       <c r="E365" s="5" t="n">
-        <v>137.24</v>
+        <v>30.51</v>
       </c>
       <c r="F365" s="7" t="n">
         <v>-1.61</v>
@@ -10059,12 +10059,12 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>Huntington Bancshares</t>
+          <t>FactSet</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="D371" s="5" t="n">
-        <v>18.56</v>
+        <v>262.46</v>
       </c>
       <c r="E371" s="5" t="n">
-        <v>18.25</v>
+        <v>258.09</v>
       </c>
       <c r="F371" s="7" t="n">
         <v>-1.67</v>
@@ -10085,24 +10085,24 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>FactSet</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D372" s="5" t="n">
-        <v>262.46</v>
+        <v>108.29</v>
       </c>
       <c r="E372" s="5" t="n">
-        <v>258.09</v>
+        <v>106.48</v>
       </c>
       <c r="F372" s="7" t="n">
         <v>-1.67</v>
@@ -10111,24 +10111,24 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Fidelity National Information Services</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D373" s="5" t="n">
-        <v>108.29</v>
+        <v>42.62</v>
       </c>
       <c r="E373" s="5" t="n">
-        <v>106.48</v>
+        <v>41.91</v>
       </c>
       <c r="F373" s="7" t="n">
         <v>-1.67</v>
@@ -10137,12 +10137,12 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>Fidelity National Information Services</t>
+          <t>Huntington Bancshares</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>42.62</v>
+        <v>18.56</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>41.91</v>
+        <v>18.25</v>
       </c>
       <c r="F374" s="7" t="n">
         <v>-1.67</v>
@@ -10241,24 +10241,24 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>J.M. Smucker Company (The)</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D378" s="5" t="n">
-        <v>361.57</v>
+        <v>113.97</v>
       </c>
       <c r="E378" s="5" t="n">
-        <v>355.35</v>
+        <v>112.01</v>
       </c>
       <c r="F378" s="7" t="n">
         <v>-1.72</v>
@@ -10267,24 +10267,24 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>J.M. Smucker Company (The)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D379" s="5" t="n">
-        <v>113.97</v>
+        <v>361.57</v>
       </c>
       <c r="E379" s="5" t="n">
-        <v>112.01</v>
+        <v>355.35</v>
       </c>
       <c r="F379" s="7" t="n">
         <v>-1.72</v>
@@ -10371,24 +10371,24 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Mosaic Company (The)</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D383" s="5" t="n">
-        <v>131.71</v>
+        <v>22.53</v>
       </c>
       <c r="E383" s="5" t="n">
-        <v>129.36</v>
+        <v>22.13</v>
       </c>
       <c r="F383" s="7" t="n">
         <v>-1.78</v>
@@ -10397,24 +10397,24 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Company (The)</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D384" s="5" t="n">
-        <v>22.53</v>
+        <v>131.71</v>
       </c>
       <c r="E384" s="5" t="n">
-        <v>22.13</v>
+        <v>129.36</v>
       </c>
       <c r="F384" s="7" t="n">
         <v>-1.78</v>
@@ -10475,24 +10475,24 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>Nike, Inc.</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D387" s="5" t="n">
-        <v>44.57</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>43.76</v>
+        <v>90.53</v>
       </c>
       <c r="F387" s="7" t="n">
         <v>-1.82</v>
@@ -10501,24 +10501,24 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D388" s="5" t="n">
-        <v>92.20999999999999</v>
+        <v>401.1</v>
       </c>
       <c r="E388" s="5" t="n">
-        <v>90.53</v>
+        <v>393.82</v>
       </c>
       <c r="F388" s="7" t="n">
         <v>-1.82</v>
@@ -10527,24 +10527,24 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nike, Inc.</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>401.1</v>
+        <v>44.57</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>393.82</v>
+        <v>43.76</v>
       </c>
       <c r="F389" s="7" t="n">
         <v>-1.82</v>
@@ -10605,24 +10605,24 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>ResMed</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D392" s="5" t="n">
-        <v>80.14</v>
+        <v>202.76</v>
       </c>
       <c r="E392" s="5" t="n">
-        <v>78.65000000000001</v>
+        <v>198.99</v>
       </c>
       <c r="F392" s="7" t="n">
         <v>-1.86</v>
@@ -10631,24 +10631,24 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>ResMed</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>202.76</v>
+        <v>80.14</v>
       </c>
       <c r="E393" s="5" t="n">
-        <v>198.99</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>-1.86</v>
@@ -10683,12 +10683,12 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Hershey Company (The)</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
@@ -10697,10 +10697,10 @@
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>174.72</v>
+        <v>38.7</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>171.42</v>
+        <v>37.97</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>-1.89</v>
@@ -10735,24 +10735,24 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Hershey Company (The)</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D397" s="5" t="n">
-        <v>142.89</v>
+        <v>174.72</v>
       </c>
       <c r="E397" s="5" t="n">
-        <v>140.19</v>
+        <v>171.42</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>-1.89</v>
@@ -10761,24 +10761,24 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D398" s="5" t="n">
-        <v>38.7</v>
+        <v>142.89</v>
       </c>
       <c r="E398" s="5" t="n">
-        <v>37.97</v>
+        <v>140.19</v>
       </c>
       <c r="F398" s="7" t="n">
         <v>-1.89</v>
@@ -10813,24 +10813,24 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>CBRE Group</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D400" s="5" t="n">
-        <v>73.09999999999999</v>
+        <v>143.69</v>
       </c>
       <c r="E400" s="5" t="n">
-        <v>71.70999999999999</v>
+        <v>140.96</v>
       </c>
       <c r="F400" s="7" t="n">
         <v>-1.9</v>
@@ -10839,24 +10839,24 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>CBRE Group</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D401" s="5" t="n">
-        <v>143.69</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E401" s="5" t="n">
-        <v>140.96</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>-1.9</v>
@@ -11151,24 +11151,24 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>44.84</v>
+        <v>125.3</v>
       </c>
       <c r="E413" s="5" t="n">
-        <v>43.94</v>
+        <v>122.78</v>
       </c>
       <c r="F413" s="7" t="n">
         <v>-2.01</v>
@@ -11203,24 +11203,24 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>125.3</v>
+        <v>44.84</v>
       </c>
       <c r="E415" s="5" t="n">
-        <v>122.78</v>
+        <v>43.94</v>
       </c>
       <c r="F415" s="7" t="n">
         <v>-2.01</v>
@@ -11385,24 +11385,24 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>Lululemon Athletica</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D422" s="5" t="n">
-        <v>118.79</v>
+        <v>75</v>
       </c>
       <c r="E422" s="5" t="n">
-        <v>116.33</v>
+        <v>73.45</v>
       </c>
       <c r="F422" s="7" t="n">
         <v>-2.07</v>
@@ -11411,24 +11411,24 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>Lululemon Athletica</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D423" s="5" t="n">
-        <v>75</v>
+        <v>118.79</v>
       </c>
       <c r="E423" s="5" t="n">
-        <v>73.45</v>
+        <v>116.33</v>
       </c>
       <c r="F423" s="7" t="n">
         <v>-2.07</v>
@@ -11437,24 +11437,24 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D424" s="5" t="n">
-        <v>273.46</v>
+        <v>135.72</v>
       </c>
       <c r="E424" s="5" t="n">
-        <v>267.71</v>
+        <v>132.87</v>
       </c>
       <c r="F424" s="7" t="n">
         <v>-2.1</v>
@@ -11463,24 +11463,24 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Franklin Resources</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>135.72</v>
+        <v>33.33</v>
       </c>
       <c r="E425" s="5" t="n">
-        <v>132.87</v>
+        <v>32.63</v>
       </c>
       <c r="F425" s="7" t="n">
         <v>-2.1</v>
@@ -11489,24 +11489,24 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D426" s="5" t="n">
-        <v>160.49</v>
+        <v>229.16</v>
       </c>
       <c r="E426" s="5" t="n">
-        <v>157.12</v>
+        <v>224.35</v>
       </c>
       <c r="F426" s="7" t="n">
         <v>-2.1</v>
@@ -11515,12 +11515,12 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>Franklin Resources</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="D427" s="5" t="n">
-        <v>33.33</v>
+        <v>160.49</v>
       </c>
       <c r="E427" s="5" t="n">
-        <v>32.63</v>
+        <v>157.12</v>
       </c>
       <c r="F427" s="7" t="n">
         <v>-2.1</v>
@@ -11541,24 +11541,24 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D428" s="5" t="n">
-        <v>229.16</v>
+        <v>273.46</v>
       </c>
       <c r="E428" s="5" t="n">
-        <v>224.35</v>
+        <v>267.71</v>
       </c>
       <c r="F428" s="7" t="n">
         <v>-2.1</v>
@@ -11567,24 +11567,24 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>63.15</v>
+        <v>51.72</v>
       </c>
       <c r="E429" s="5" t="n">
-        <v>61.82</v>
+        <v>50.63</v>
       </c>
       <c r="F429" s="7" t="n">
         <v>-2.11</v>
@@ -11593,24 +11593,24 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D430" s="5" t="n">
-        <v>51.72</v>
+        <v>63.15</v>
       </c>
       <c r="E430" s="5" t="n">
-        <v>50.63</v>
+        <v>61.82</v>
       </c>
       <c r="F430" s="7" t="n">
         <v>-2.11</v>
@@ -11671,12 +11671,12 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class C)</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C433" s="4" t="inlineStr">
@@ -11685,10 +11685,10 @@
         </is>
       </c>
       <c r="D433" s="5" t="n">
-        <v>353.81</v>
+        <v>354.46</v>
       </c>
       <c r="E433" s="5" t="n">
-        <v>346.12</v>
+        <v>346.77</v>
       </c>
       <c r="F433" s="7" t="n">
         <v>-2.17</v>
@@ -11697,12 +11697,12 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
       <c r="C434" s="4" t="inlineStr">
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="D434" s="5" t="n">
-        <v>354.46</v>
+        <v>353.81</v>
       </c>
       <c r="E434" s="5" t="n">
-        <v>346.77</v>
+        <v>346.12</v>
       </c>
       <c r="F434" s="7" t="n">
         <v>-2.17</v>
@@ -11775,24 +11775,24 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>McCormick &amp; Company</t>
         </is>
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D437" s="5" t="n">
-        <v>329.67</v>
+        <v>52.9</v>
       </c>
       <c r="E437" s="5" t="n">
-        <v>322.18</v>
+        <v>51.7</v>
       </c>
       <c r="F437" s="7" t="n">
         <v>-2.27</v>
@@ -11801,24 +11801,24 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>McCormick &amp; Company</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D438" s="5" t="n">
-        <v>52.9</v>
+        <v>329.67</v>
       </c>
       <c r="E438" s="5" t="n">
-        <v>51.7</v>
+        <v>322.18</v>
       </c>
       <c r="F438" s="7" t="n">
         <v>-2.27</v>
@@ -11957,24 +11957,24 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D444" s="5" t="n">
-        <v>109.03</v>
+        <v>123.34</v>
       </c>
       <c r="E444" s="5" t="n">
-        <v>106.49</v>
+        <v>120.47</v>
       </c>
       <c r="F444" s="7" t="n">
         <v>-2.33</v>
@@ -11983,24 +11983,24 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>Apollo Global Management</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D445" s="5" t="n">
-        <v>123.34</v>
+        <v>109.03</v>
       </c>
       <c r="E445" s="5" t="n">
-        <v>120.47</v>
+        <v>106.49</v>
       </c>
       <c r="F445" s="7" t="n">
         <v>-2.33</v>
@@ -12139,24 +12139,24 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>Copart</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D451" s="5" t="n">
-        <v>28.29</v>
+        <v>87.84</v>
       </c>
       <c r="E451" s="5" t="n">
-        <v>27.61</v>
+        <v>85.73</v>
       </c>
       <c r="F451" s="7" t="n">
         <v>-2.4</v>
@@ -12165,24 +12165,24 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Copart</t>
         </is>
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D452" s="5" t="n">
-        <v>87.84</v>
+        <v>28.29</v>
       </c>
       <c r="E452" s="5" t="n">
-        <v>85.73</v>
+        <v>27.61</v>
       </c>
       <c r="F452" s="7" t="n">
         <v>-2.4</v>
@@ -12659,24 +12659,24 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Trade Desk (The)</t>
         </is>
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D471" s="5" t="n">
-        <v>94.25</v>
+        <v>19.12</v>
       </c>
       <c r="E471" s="5" t="n">
-        <v>91.64</v>
+        <v>18.59</v>
       </c>
       <c r="F471" s="7" t="n">
         <v>-2.77</v>
@@ -12685,24 +12685,24 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>Trade Desk (The)</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D472" s="5" t="n">
-        <v>19.12</v>
+        <v>94.25</v>
       </c>
       <c r="E472" s="5" t="n">
-        <v>18.59</v>
+        <v>91.64</v>
       </c>
       <c r="F472" s="7" t="n">
         <v>-2.77</v>
@@ -12945,24 +12945,24 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D482" s="5" t="n">
-        <v>59.26</v>
+        <v>219.37</v>
       </c>
       <c r="E482" s="5" t="n">
-        <v>57.47</v>
+        <v>212.75</v>
       </c>
       <c r="F482" s="7" t="n">
         <v>-3.02</v>
@@ -12971,24 +12971,24 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D483" s="5" t="n">
-        <v>219.37</v>
+        <v>59.26</v>
       </c>
       <c r="E483" s="5" t="n">
-        <v>212.75</v>
+        <v>57.47</v>
       </c>
       <c r="F483" s="7" t="n">
         <v>-3.02</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 10 close to Jul 17 close  |  503 companies  |  updated 2026-07-19 04:06</t>
+          <t>Jul 10 close to Jul 17 close  |  503 companies  |  updated 2026-07-20 04:12</t>
         </is>
       </c>
     </row>
@@ -15755,30 +15755,30 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>120.94</v>
+        <v>138.95</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>126.02</v>
+        <v>144.78</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>126.02</v>
+        <v>145.43</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>120.94</v>
+        <v>138.95</v>
       </c>
       <c r="H69" s="6" t="n">
         <v>4.2</v>
@@ -15787,30 +15787,30 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Federal Realty Investment Trust</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>138.95</v>
+        <v>120.94</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>144.78</v>
+        <v>126.02</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>145.43</v>
+        <v>126.02</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>138.95</v>
+        <v>120.94</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>4.2</v>
@@ -16619,12 +16619,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Gilead Sciences</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -16633,16 +16633,16 @@
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>199.15</v>
+        <v>129.83</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>205.99</v>
+        <v>134.28</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>209.03</v>
+        <v>136.3</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>191.95</v>
+        <v>129.83</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>3.43</v>
@@ -16651,12 +16651,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Gilead Sciences</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -16665,16 +16665,16 @@
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>129.83</v>
+        <v>199.15</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>134.28</v>
+        <v>205.99</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>136.3</v>
+        <v>209.03</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>129.83</v>
+        <v>191.95</v>
       </c>
       <c r="H97" s="6" t="n">
         <v>3.43</v>
@@ -17099,30 +17099,30 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Merck &amp; Co.</t>
+          <t>Prudential Financial</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>123.54</v>
+        <v>115.37</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>127.5</v>
+        <v>119.07</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>127.63</v>
+        <v>119.07</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>120.78</v>
+        <v>114.79</v>
       </c>
       <c r="H111" s="6" t="n">
         <v>3.21</v>
@@ -17131,30 +17131,30 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Prudential Financial</t>
+          <t>Merck &amp; Co.</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>115.37</v>
+        <v>123.54</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>119.07</v>
+        <v>127.5</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>119.07</v>
+        <v>127.63</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>114.79</v>
+        <v>120.78</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>3.21</v>
@@ -17163,30 +17163,30 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Gen Digital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>25.91</v>
+        <v>526.74</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>26.74</v>
+        <v>543.6</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>27.01</v>
+        <v>551.54</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>25.91</v>
+        <v>526.74</v>
       </c>
       <c r="H113" s="6" t="n">
         <v>3.2</v>
@@ -17195,30 +17195,30 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Gen Digital</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>526.74</v>
+        <v>25.91</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>543.6</v>
+        <v>26.74</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>551.54</v>
+        <v>27.01</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>526.74</v>
+        <v>25.91</v>
       </c>
       <c r="H114" s="6" t="n">
         <v>3.2</v>
@@ -17355,30 +17355,30 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Steel Dynamics</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>228.42</v>
+        <v>123.09</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>235.51</v>
+        <v>126.91</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>235.56</v>
+        <v>128.97</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>228.42</v>
+        <v>122.04</v>
       </c>
       <c r="H119" s="6" t="n">
         <v>3.1</v>
@@ -17387,30 +17387,30 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Steel Dynamics</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>123.09</v>
+        <v>228.42</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>126.91</v>
+        <v>235.51</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>128.97</v>
+        <v>235.56</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>122.04</v>
+        <v>228.42</v>
       </c>
       <c r="H120" s="6" t="n">
         <v>3.1</v>
@@ -18059,30 +18059,30 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Waste Management</t>
+          <t>HP Inc.</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>233.33</v>
+        <v>24.22</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>239.31</v>
+        <v>24.84</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>242.25</v>
+        <v>24.84</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>232.8</v>
+        <v>23.75</v>
       </c>
       <c r="H141" s="6" t="n">
         <v>2.56</v>
@@ -18123,30 +18123,30 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>HP Inc.</t>
+          <t>Waste Management</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>24.22</v>
+        <v>233.33</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>24.84</v>
+        <v>239.31</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>24.84</v>
+        <v>242.25</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>23.75</v>
+        <v>232.8</v>
       </c>
       <c r="H143" s="6" t="n">
         <v>2.56</v>
@@ -18507,30 +18507,30 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>88.22</v>
+        <v>469.2</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>90.17</v>
+        <v>479.57</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>91.31</v>
+        <v>479.57</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>86.53</v>
+        <v>466.14</v>
       </c>
       <c r="H155" s="6" t="n">
         <v>2.21</v>
@@ -18539,30 +18539,30 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
-        <v>469.2</v>
+        <v>88.22</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>479.57</v>
+        <v>90.17</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>479.57</v>
+        <v>91.31</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>466.14</v>
+        <v>86.53</v>
       </c>
       <c r="H156" s="6" t="n">
         <v>2.21</v>
@@ -19115,30 +19115,30 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>586.86</v>
+        <v>96.36</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>597.24</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>598.97</v>
+        <v>99.12</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>584.4</v>
+        <v>95.41</v>
       </c>
       <c r="H174" s="6" t="n">
         <v>1.77</v>
@@ -19147,30 +19147,30 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>96.36</v>
+        <v>586.86</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>597.24</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>99.12</v>
+        <v>598.97</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>95.41</v>
+        <v>584.4</v>
       </c>
       <c r="H175" s="6" t="n">
         <v>1.77</v>
@@ -19339,30 +19339,30 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
-        <v>147.47</v>
+        <v>57.07</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>149.91</v>
+        <v>58.01</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>153.06</v>
+        <v>59.37</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>146.02</v>
+        <v>57.05</v>
       </c>
       <c r="H181" s="6" t="n">
         <v>1.65</v>
@@ -19371,30 +19371,30 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Broadridge Financial Solutions</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>57.07</v>
+        <v>147.47</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>58.01</v>
+        <v>149.91</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>59.37</v>
+        <v>153.06</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>57.05</v>
+        <v>146.02</v>
       </c>
       <c r="H182" s="6" t="n">
         <v>1.65</v>
@@ -19595,30 +19595,30 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
-        <v>303.44</v>
+        <v>157.52</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>307.9</v>
+        <v>159.84</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>307.99</v>
+        <v>161.77</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>296.57</v>
+        <v>156.58</v>
       </c>
       <c r="H189" s="6" t="n">
         <v>1.47</v>
@@ -19627,30 +19627,30 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>157.52</v>
+        <v>303.44</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>159.84</v>
+        <v>307.9</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>161.77</v>
+        <v>307.99</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>156.58</v>
+        <v>296.57</v>
       </c>
       <c r="H190" s="6" t="n">
         <v>1.47</v>
@@ -20011,12 +20011,12 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Ametek</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -20025,16 +20025,16 @@
         </is>
       </c>
       <c r="D202" s="5" t="n">
-        <v>233.98</v>
+        <v>121.22</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>237</v>
+        <v>122.78</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>237.3</v>
+        <v>125.3</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>232.1</v>
+        <v>121.21</v>
       </c>
       <c r="H202" s="6" t="n">
         <v>1.29</v>
@@ -20043,12 +20043,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Ametek</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -20057,16 +20057,16 @@
         </is>
       </c>
       <c r="D203" s="5" t="n">
-        <v>121.22</v>
+        <v>233.98</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>122.78</v>
+        <v>237</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>125.3</v>
+        <v>237.3</v>
       </c>
       <c r="G203" s="5" t="n">
-        <v>121.21</v>
+        <v>232.1</v>
       </c>
       <c r="H203" s="6" t="n">
         <v>1.29</v>
@@ -20395,30 +20395,30 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>KeyCorp</t>
+          <t>PulteGroup</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D214" s="5" t="n">
-        <v>23.3</v>
+        <v>124.75</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>23.55</v>
+        <v>126.08</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>23.99</v>
+        <v>129.02</v>
       </c>
       <c r="G214" s="5" t="n">
-        <v>23.22</v>
+        <v>123.75</v>
       </c>
       <c r="H214" s="6" t="n">
         <v>1.07</v>
@@ -20459,12 +20459,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Hartford (The)</t>
+          <t>KeyCorp</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -20473,16 +20473,16 @@
         </is>
       </c>
       <c r="D216" s="5" t="n">
-        <v>138.78</v>
+        <v>23.3</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>140.26</v>
+        <v>23.55</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>140.78</v>
+        <v>23.99</v>
       </c>
       <c r="G216" s="5" t="n">
-        <v>134.5</v>
+        <v>23.22</v>
       </c>
       <c r="H216" s="6" t="n">
         <v>1.07</v>
@@ -20491,30 +20491,30 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>PulteGroup</t>
+          <t>Hartford (The)</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
-        <v>124.75</v>
+        <v>138.78</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>126.08</v>
+        <v>140.26</v>
       </c>
       <c r="F217" s="5" t="n">
-        <v>129.02</v>
+        <v>140.78</v>
       </c>
       <c r="G217" s="5" t="n">
-        <v>123.75</v>
+        <v>134.5</v>
       </c>
       <c r="H217" s="6" t="n">
         <v>1.07</v>
@@ -20683,30 +20683,30 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>1055.18</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>88.8</v>
+        <v>1065.22</v>
       </c>
       <c r="F223" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>1152.07</v>
       </c>
       <c r="G223" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>1045.91</v>
       </c>
       <c r="H223" s="6" t="n">
         <v>0.95</v>
@@ -20715,30 +20715,30 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D224" s="5" t="n">
-        <v>1055.18</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>1065.22</v>
+        <v>88.8</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>1152.07</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1045.91</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="H224" s="6" t="n">
         <v>0.95</v>
@@ -21067,30 +21067,30 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
-        <v>363.39</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>366.29</v>
+        <v>92.98</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>371.58</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="G235" s="5" t="n">
-        <v>355.25</v>
+        <v>91.03</v>
       </c>
       <c r="H235" s="6" t="n">
         <v>0.8</v>
@@ -21099,30 +21099,30 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D236" s="5" t="n">
-        <v>92.23999999999999</v>
+        <v>363.39</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>92.98</v>
+        <v>366.29</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>94.06999999999999</v>
+        <v>371.58</v>
       </c>
       <c r="G236" s="5" t="n">
-        <v>91.03</v>
+        <v>355.25</v>
       </c>
       <c r="H236" s="6" t="n">
         <v>0.8</v>
@@ -21611,30 +21611,30 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D252" s="5" t="n">
-        <v>134.68</v>
+        <v>257.54</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>135.29</v>
+        <v>258.69</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>135.29</v>
+        <v>270.73</v>
       </c>
       <c r="G252" s="5" t="n">
-        <v>132.66</v>
+        <v>257.54</v>
       </c>
       <c r="H252" s="6" t="n">
         <v>0.45</v>
@@ -21643,30 +21643,30 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>EQR</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Equity Residential</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>68.69</v>
+        <v>134.68</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>69</v>
+        <v>135.29</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>70</v>
+        <v>135.29</v>
       </c>
       <c r="G253" s="5" t="n">
-        <v>68.26000000000001</v>
+        <v>132.66</v>
       </c>
       <c r="H253" s="6" t="n">
         <v>0.45</v>
@@ -21675,30 +21675,30 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D254" s="5" t="n">
-        <v>257.54</v>
+        <v>136.63</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>258.69</v>
+        <v>137.24</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>270.73</v>
+        <v>139.48</v>
       </c>
       <c r="G254" s="5" t="n">
-        <v>257.54</v>
+        <v>135.82</v>
       </c>
       <c r="H254" s="6" t="n">
         <v>0.45</v>
@@ -21707,30 +21707,30 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>EQR</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Equity Residential</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>136.63</v>
+        <v>68.69</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>137.24</v>
+        <v>69</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>139.48</v>
+        <v>70</v>
       </c>
       <c r="G255" s="5" t="n">
-        <v>135.82</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="H255" s="6" t="n">
         <v>0.45</v>
@@ -21739,30 +21739,30 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>87.16</v>
+        <v>251.38</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>87.51000000000001</v>
+        <v>252.39</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>88.06999999999999</v>
+        <v>258.12</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>85.29000000000001</v>
+        <v>251.38</v>
       </c>
       <c r="H256" s="6" t="n">
         <v>0.4</v>
@@ -21771,30 +21771,30 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
-        <v>184.4</v>
+        <v>87.16</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>185.13</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>185.7</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="G257" s="5" t="n">
-        <v>180.96</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H257" s="6" t="n">
         <v>0.4</v>
@@ -21803,30 +21803,30 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D258" s="5" t="n">
-        <v>251.38</v>
+        <v>184.4</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>252.39</v>
+        <v>185.13</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>258.12</v>
+        <v>185.7</v>
       </c>
       <c r="G258" s="5" t="n">
-        <v>251.38</v>
+        <v>180.96</v>
       </c>
       <c r="H258" s="6" t="n">
         <v>0.4</v>
@@ -21995,12 +21995,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Copart</t>
+          <t>Wabtec</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -22009,16 +22009,16 @@
         </is>
       </c>
       <c r="D264" s="5" t="n">
-        <v>27.52</v>
+        <v>261.21</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>27.61</v>
+        <v>262.08</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>28.29</v>
+        <v>263.89</v>
       </c>
       <c r="G264" s="5" t="n">
-        <v>27.28</v>
+        <v>259.71</v>
       </c>
       <c r="H264" s="6" t="n">
         <v>0.33</v>
@@ -22027,12 +22027,12 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Wabtec</t>
+          <t>Copart</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -22041,16 +22041,16 @@
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>261.21</v>
+        <v>27.52</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>262.08</v>
+        <v>27.61</v>
       </c>
       <c r="F265" s="5" t="n">
-        <v>263.89</v>
+        <v>28.29</v>
       </c>
       <c r="G265" s="5" t="n">
-        <v>259.71</v>
+        <v>27.28</v>
       </c>
       <c r="H265" s="6" t="n">
         <v>0.33</v>
@@ -22315,30 +22315,30 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D274" s="5" t="n">
-        <v>168.12</v>
+        <v>634.6</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>168.36</v>
+        <v>635.52</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>170.3</v>
+        <v>635.52</v>
       </c>
       <c r="G274" s="5" t="n">
-        <v>166.98</v>
+        <v>623.1</v>
       </c>
       <c r="H274" s="6" t="n">
         <v>0.14</v>
@@ -22347,30 +22347,30 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
-        <v>634.6</v>
+        <v>168.12</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>635.52</v>
+        <v>168.36</v>
       </c>
       <c r="F275" s="5" t="n">
-        <v>635.52</v>
+        <v>170.3</v>
       </c>
       <c r="G275" s="5" t="n">
-        <v>623.1</v>
+        <v>166.98</v>
       </c>
       <c r="H275" s="6" t="n">
         <v>0.14</v>
@@ -22699,30 +22699,30 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>Trimble Inc.</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D286" s="5" t="n">
-        <v>160.71</v>
+        <v>52.82</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>160.41</v>
+        <v>52.72</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>163.06</v>
+        <v>53.75</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>156.79</v>
+        <v>51.58</v>
       </c>
       <c r="H286" s="7" t="n">
         <v>-0.19</v>
@@ -22731,30 +22731,30 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
-        <v>52.82</v>
+        <v>160.71</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>52.72</v>
+        <v>160.41</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>53.75</v>
+        <v>163.06</v>
       </c>
       <c r="G287" s="5" t="n">
-        <v>51.58</v>
+        <v>156.79</v>
       </c>
       <c r="H287" s="7" t="n">
         <v>-0.19</v>
@@ -22923,30 +22923,30 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>O’Reilly Automotive</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>86.28</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>86.05</v>
+        <v>74.62</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>87.28</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>82.73</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="H293" s="7" t="n">
         <v>-0.27</v>
@@ -22955,30 +22955,30 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>O’Reilly Automotive</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>74.81999999999999</v>
+        <v>86.28</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>74.62</v>
+        <v>86.05</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>75.04000000000001</v>
+        <v>87.28</v>
       </c>
       <c r="G294" s="5" t="n">
-        <v>73.79000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="H294" s="7" t="n">
         <v>-0.27</v>
@@ -23307,30 +23307,30 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
-        <v>314.69</v>
+        <v>274.31</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>312.98</v>
+        <v>272.83</v>
       </c>
       <c r="F305" s="5" t="n">
-        <v>318.2</v>
+        <v>275.71</v>
       </c>
       <c r="G305" s="5" t="n">
-        <v>312.98</v>
+        <v>269.75</v>
       </c>
       <c r="H305" s="7" t="n">
         <v>-0.54</v>
@@ -23339,30 +23339,30 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>274.31</v>
+        <v>314.69</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>272.83</v>
+        <v>312.98</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>275.71</v>
+        <v>318.2</v>
       </c>
       <c r="G306" s="5" t="n">
-        <v>269.75</v>
+        <v>312.98</v>
       </c>
       <c r="H306" s="7" t="n">
         <v>-0.54</v>
@@ -23467,30 +23467,30 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Estée Lauder Companies (The)</t>
+          <t>Genuine Parts Company</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D310" s="5" t="n">
-        <v>82.66</v>
+        <v>125.62</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>82.13</v>
+        <v>124.82</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>82.84</v>
+        <v>125.66</v>
       </c>
       <c r="G310" s="5" t="n">
-        <v>80.86</v>
+        <v>121</v>
       </c>
       <c r="H310" s="7" t="n">
         <v>-0.64</v>
@@ -23499,30 +23499,30 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Genuine Parts Company</t>
+          <t>Estée Lauder Companies (The)</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
-        <v>125.62</v>
+        <v>82.66</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>124.82</v>
+        <v>82.13</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>125.66</v>
+        <v>82.84</v>
       </c>
       <c r="G311" s="5" t="n">
-        <v>121</v>
+        <v>80.86</v>
       </c>
       <c r="H311" s="7" t="n">
         <v>-0.64</v>
@@ -23659,30 +23659,30 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D316" s="5" t="n">
-        <v>19.61</v>
+        <v>207.85</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>19.46</v>
+        <v>206.26</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>19.73</v>
+        <v>210.49</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>19.46</v>
+        <v>206.26</v>
       </c>
       <c r="H316" s="7" t="n">
         <v>-0.76</v>
@@ -23691,30 +23691,30 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Norwegian Cruise Line Holdings</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D317" s="5" t="n">
-        <v>207.85</v>
+        <v>19.61</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>206.26</v>
+        <v>19.46</v>
       </c>
       <c r="F317" s="5" t="n">
-        <v>210.49</v>
+        <v>19.73</v>
       </c>
       <c r="G317" s="5" t="n">
-        <v>206.26</v>
+        <v>19.46</v>
       </c>
       <c r="H317" s="7" t="n">
         <v>-0.76</v>
@@ -23787,30 +23787,30 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation</t>
+          <t>Lilly (Eli)</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>72.19</v>
+        <v>1188.58</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>71.61</v>
+        <v>1179.11</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>73.84</v>
+        <v>1188.58</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>69.88</v>
+        <v>1152.54</v>
       </c>
       <c r="H320" s="7" t="n">
         <v>-0.8</v>
@@ -23819,30 +23819,30 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>333.99</v>
+        <v>83.87</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>331.32</v>
+        <v>83.2</v>
       </c>
       <c r="F321" s="5" t="n">
-        <v>338.14</v>
+        <v>83.87</v>
       </c>
       <c r="G321" s="5" t="n">
-        <v>328.5</v>
+        <v>79.3</v>
       </c>
       <c r="H321" s="7" t="n">
         <v>-0.8</v>
@@ -23851,30 +23851,30 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Lilly (Eli)</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D322" s="5" t="n">
-        <v>1188.58</v>
+        <v>333.99</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>1179.11</v>
+        <v>331.32</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>1188.58</v>
+        <v>338.14</v>
       </c>
       <c r="G322" s="5" t="n">
-        <v>1152.54</v>
+        <v>328.5</v>
       </c>
       <c r="H322" s="7" t="n">
         <v>-0.8</v>
@@ -23883,30 +23883,30 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>W. R. Berkley Corporation</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D323" s="5" t="n">
-        <v>83.87</v>
+        <v>72.19</v>
       </c>
       <c r="E323" s="5" t="n">
-        <v>83.2</v>
+        <v>71.61</v>
       </c>
       <c r="F323" s="5" t="n">
-        <v>83.87</v>
+        <v>73.84</v>
       </c>
       <c r="G323" s="5" t="n">
-        <v>79.3</v>
+        <v>69.88</v>
       </c>
       <c r="H323" s="7" t="n">
         <v>-0.8</v>
@@ -24011,30 +24011,30 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Carrier Global</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>69.34</v>
+        <v>43.54</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>68.69</v>
+        <v>43.13</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>69.76000000000001</v>
+        <v>44.13</v>
       </c>
       <c r="G327" s="5" t="n">
-        <v>68.61</v>
+        <v>42.72</v>
       </c>
       <c r="H327" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -24043,30 +24043,30 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Carrier Global</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>43.54</v>
+        <v>69.34</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>43.13</v>
+        <v>68.69</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>44.13</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="G328" s="5" t="n">
-        <v>42.72</v>
+        <v>68.61</v>
       </c>
       <c r="H328" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -24171,30 +24171,30 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D332" s="5" t="n">
-        <v>159.07</v>
+        <v>112.94</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>157.12</v>
+        <v>111.55</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>167.21</v>
+        <v>113.43</v>
       </c>
       <c r="G332" s="5" t="n">
-        <v>157.12</v>
+        <v>111.38</v>
       </c>
       <c r="H332" s="7" t="n">
         <v>-1.23</v>
@@ -24203,30 +24203,30 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>112.94</v>
+        <v>159.07</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>111.55</v>
+        <v>157.12</v>
       </c>
       <c r="F333" s="5" t="n">
-        <v>113.43</v>
+        <v>167.21</v>
       </c>
       <c r="G333" s="5" t="n">
-        <v>111.38</v>
+        <v>157.12</v>
       </c>
       <c r="H333" s="7" t="n">
         <v>-1.23</v>
@@ -24267,30 +24267,30 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Hershey Company (The)</t>
+          <t>Home Depot (The)</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>173.66</v>
+        <v>343.3</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>171.42</v>
+        <v>338.87</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>175.24</v>
+        <v>348.02</v>
       </c>
       <c r="G335" s="5" t="n">
-        <v>170.27</v>
+        <v>337.11</v>
       </c>
       <c r="H335" s="7" t="n">
         <v>-1.29</v>
@@ -24299,30 +24299,30 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Home Depot (The)</t>
+          <t>Hershey Company (The)</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>343.3</v>
+        <v>173.66</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>338.87</v>
+        <v>171.42</v>
       </c>
       <c r="F336" s="5" t="n">
-        <v>348.02</v>
+        <v>175.24</v>
       </c>
       <c r="G336" s="5" t="n">
-        <v>337.11</v>
+        <v>170.27</v>
       </c>
       <c r="H336" s="7" t="n">
         <v>-1.29</v>
@@ -24715,30 +24715,30 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>26.83</v>
+        <v>115.05</v>
       </c>
       <c r="E349" s="5" t="n">
-        <v>26.41</v>
+        <v>113.24</v>
       </c>
       <c r="F349" s="5" t="n">
-        <v>26.86</v>
+        <v>115.41</v>
       </c>
       <c r="G349" s="5" t="n">
-        <v>26.41</v>
+        <v>113.24</v>
       </c>
       <c r="H349" s="7" t="n">
         <v>-1.57</v>
@@ -24747,30 +24747,30 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D350" s="5" t="n">
-        <v>115.05</v>
+        <v>26.83</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>113.24</v>
+        <v>26.41</v>
       </c>
       <c r="F350" s="5" t="n">
-        <v>115.41</v>
+        <v>26.86</v>
       </c>
       <c r="G350" s="5" t="n">
-        <v>113.24</v>
+        <v>26.41</v>
       </c>
       <c r="H350" s="7" t="n">
         <v>-1.57</v>
@@ -24811,30 +24811,30 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D352" s="5" t="n">
-        <v>47.76</v>
+        <v>80.06</v>
       </c>
       <c r="E352" s="5" t="n">
-        <v>46.99</v>
+        <v>78.77</v>
       </c>
       <c r="F352" s="5" t="n">
-        <v>47.76</v>
+        <v>80.48</v>
       </c>
       <c r="G352" s="5" t="n">
-        <v>46.99</v>
+        <v>78.77</v>
       </c>
       <c r="H352" s="7" t="n">
         <v>-1.61</v>
@@ -24843,30 +24843,30 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>80.06</v>
+        <v>47.76</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>78.77</v>
+        <v>46.99</v>
       </c>
       <c r="F353" s="5" t="n">
-        <v>80.48</v>
+        <v>47.76</v>
       </c>
       <c r="G353" s="5" t="n">
-        <v>78.77</v>
+        <v>46.99</v>
       </c>
       <c r="H353" s="7" t="n">
         <v>-1.61</v>
@@ -25995,30 +25995,30 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>274.6</v>
+        <v>355.03</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>267.71</v>
+        <v>346.12</v>
       </c>
       <c r="F389" s="5" t="n">
-        <v>274.6</v>
+        <v>370.21</v>
       </c>
       <c r="G389" s="5" t="n">
-        <v>264.95</v>
+        <v>346.12</v>
       </c>
       <c r="H389" s="7" t="n">
         <v>-2.51</v>
@@ -26027,30 +26027,30 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class C)</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D390" s="5" t="n">
-        <v>355.03</v>
+        <v>274.6</v>
       </c>
       <c r="E390" s="5" t="n">
-        <v>346.12</v>
+        <v>267.71</v>
       </c>
       <c r="F390" s="5" t="n">
-        <v>370.21</v>
+        <v>274.6</v>
       </c>
       <c r="G390" s="5" t="n">
-        <v>346.12</v>
+        <v>264.95</v>
       </c>
       <c r="H390" s="7" t="n">
         <v>-2.51</v>
@@ -26539,30 +26539,30 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>357.18</v>
+        <v>359.27</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>346.77</v>
+        <v>348.83</v>
       </c>
       <c r="F406" s="5" t="n">
-        <v>370.92</v>
+        <v>360.35</v>
       </c>
       <c r="G406" s="5" t="n">
-        <v>346.77</v>
+        <v>345.73</v>
       </c>
       <c r="H406" s="7" t="n">
         <v>-2.91</v>
@@ -26571,30 +26571,30 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>359.27</v>
+        <v>357.18</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>348.83</v>
+        <v>346.77</v>
       </c>
       <c r="F407" s="5" t="n">
-        <v>360.35</v>
+        <v>370.92</v>
       </c>
       <c r="G407" s="5" t="n">
-        <v>345.73</v>
+        <v>346.77</v>
       </c>
       <c r="H407" s="7" t="n">
         <v>-2.91</v>
@@ -26667,30 +26667,30 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Monolithic Power Systems</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D410" s="5" t="n">
-        <v>329.78</v>
+        <v>1352.74</v>
       </c>
       <c r="E410" s="5" t="n">
-        <v>319.87</v>
+        <v>1312</v>
       </c>
       <c r="F410" s="5" t="n">
-        <v>331.45</v>
+        <v>1376.41</v>
       </c>
       <c r="G410" s="5" t="n">
-        <v>311.07</v>
+        <v>1291.38</v>
       </c>
       <c r="H410" s="7" t="n">
         <v>-3.01</v>
@@ -26731,30 +26731,30 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D412" s="5" t="n">
-        <v>1352.74</v>
+        <v>329.78</v>
       </c>
       <c r="E412" s="5" t="n">
-        <v>1312</v>
+        <v>319.87</v>
       </c>
       <c r="F412" s="5" t="n">
-        <v>1376.41</v>
+        <v>331.45</v>
       </c>
       <c r="G412" s="5" t="n">
-        <v>1291.38</v>
+        <v>311.07</v>
       </c>
       <c r="H412" s="7" t="n">
         <v>-3.01</v>
@@ -28267,12 +28267,12 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C460" s="4" t="inlineStr">
@@ -28281,16 +28281,16 @@
         </is>
       </c>
       <c r="D460" s="5" t="n">
-        <v>144.39</v>
+        <v>121.31</v>
       </c>
       <c r="E460" s="5" t="n">
-        <v>133.24</v>
+        <v>111.94</v>
       </c>
       <c r="F460" s="5" t="n">
-        <v>144.39</v>
+        <v>121.31</v>
       </c>
       <c r="G460" s="5" t="n">
-        <v>130.86</v>
+        <v>109.66</v>
       </c>
       <c r="H460" s="7" t="n">
         <v>-7.72</v>
@@ -28299,12 +28299,12 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="C461" s="4" t="inlineStr">
@@ -28313,16 +28313,16 @@
         </is>
       </c>
       <c r="D461" s="5" t="n">
-        <v>121.31</v>
+        <v>144.39</v>
       </c>
       <c r="E461" s="5" t="n">
-        <v>111.94</v>
+        <v>133.24</v>
       </c>
       <c r="F461" s="5" t="n">
-        <v>121.31</v>
+        <v>144.39</v>
       </c>
       <c r="G461" s="5" t="n">
-        <v>109.66</v>
+        <v>130.86</v>
       </c>
       <c r="H461" s="7" t="n">
         <v>-7.72</v>
@@ -28907,30 +28907,30 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D480" s="5" t="n">
-        <v>565.8</v>
+        <v>186.96</v>
       </c>
       <c r="E480" s="5" t="n">
-        <v>510.28</v>
+        <v>168.61</v>
       </c>
       <c r="F480" s="5" t="n">
-        <v>565.8</v>
+        <v>186.96</v>
       </c>
       <c r="G480" s="5" t="n">
-        <v>510.28</v>
+        <v>168.56</v>
       </c>
       <c r="H480" s="7" t="n">
         <v>-9.81</v>
@@ -28939,30 +28939,30 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D481" s="5" t="n">
-        <v>186.96</v>
+        <v>565.8</v>
       </c>
       <c r="E481" s="5" t="n">
-        <v>168.61</v>
+        <v>510.28</v>
       </c>
       <c r="F481" s="5" t="n">
-        <v>186.96</v>
+        <v>565.8</v>
       </c>
       <c r="G481" s="5" t="n">
-        <v>168.56</v>
+        <v>510.28</v>
       </c>
       <c r="H481" s="7" t="n">
         <v>-9.81</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Jul 16-&gt;Jul 17) and rolling 5-day  |  updated 2026-07-19 04:06</t>
+          <t>Daily (Jul 16-&gt;Jul 17) and rolling 5-day  |  updated 2026-07-20 04:12</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 23 close to Jul 24 close  |  503 companies  |  updated 2026-07-25 03:58</t>
+          <t>Jul 23 close to Jul 24 close  |  503 companies  |  updated 2026-07-26 04:08</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
         <v>22.3</v>
       </c>
       <c r="F166" s="6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="167">
@@ -11350,7 +11350,7 @@
         <v>168.24</v>
       </c>
       <c r="E420" s="5" t="n">
-        <v>167.01</v>
+        <v>167.02</v>
       </c>
       <c r="F420" s="7" t="n">
         <v>-0.73</v>
@@ -13534,7 +13534,7 @@
         <v>205.51</v>
       </c>
       <c r="E504" s="5" t="n">
-        <v>186.5</v>
+        <v>186.51</v>
       </c>
       <c r="F504" s="7" t="n">
         <v>-9.25</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 17 close to Jul 24 close  |  503 companies  |  updated 2026-07-25 03:58</t>
+          <t>Jul 17 close to Jul 24 close  |  503 companies  |  updated 2026-07-26 04:08</t>
         </is>
       </c>
     </row>
@@ -28444,13 +28444,13 @@
         <v>176.76</v>
       </c>
       <c r="E465" s="5" t="n">
-        <v>167.01</v>
+        <v>167.02</v>
       </c>
       <c r="F465" s="5" t="n">
         <v>177.5</v>
       </c>
       <c r="G465" s="5" t="n">
-        <v>167.01</v>
+        <v>167.02</v>
       </c>
       <c r="H465" s="7" t="n">
         <v>-5.51</v>
@@ -28837,7 +28837,7 @@
         <v>21.92</v>
       </c>
       <c r="H477" s="7" t="n">
-        <v>-6.28</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="478">
@@ -29628,13 +29628,13 @@
         <v>208.5</v>
       </c>
       <c r="E502" s="5" t="n">
-        <v>186.5</v>
+        <v>186.51</v>
       </c>
       <c r="F502" s="5" t="n">
         <v>209.42</v>
       </c>
       <c r="G502" s="5" t="n">
-        <v>186.5</v>
+        <v>186.51</v>
       </c>
       <c r="H502" s="7" t="n">
         <v>-10.55</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Jul 23-&gt;Jul 24) and rolling 5-day  |  updated 2026-07-25 03:58</t>
+          <t>Daily (Jul 23-&gt;Jul 24) and rolling 5-day  |  updated 2026-07-26 04:08</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 30 close to Jul 31 close  |  503 companies  |  updated 2026-08-01 04:04</t>
+          <t>Jul 30 close to Jul 31 close  |  503 companies  |  updated 2026-08-02 04:07</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 24 close to Jul 31 close  |  503 companies  |  updated 2026-08-01 04:04</t>
+          <t>Jul 24 close to Jul 31 close  |  503 companies  |  updated 2026-08-02 04:07</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Jul 30-&gt;Jul 31) and rolling 5-day  |  updated 2026-08-01 04:04</t>
+          <t>Daily (Jul 30-&gt;Jul 31) and rolling 5-day  |  updated 2026-08-02 04:07</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 30 close to Jul 31 close  |  503 companies  |  updated 2026-08-02 04:07</t>
+          <t>Jul 30 close to Jul 31 close  |  503 companies  |  updated 2026-08-03 04:09</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 24 close to Jul 31 close  |  503 companies  |  updated 2026-08-02 04:07</t>
+          <t>Jul 24 close to Jul 31 close  |  503 companies  |  updated 2026-08-03 04:09</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Jul 30-&gt;Jul 31) and rolling 5-day  |  updated 2026-08-02 04:07</t>
+          <t>Daily (Jul 30-&gt;Jul 31) and rolling 5-day  |  updated 2026-08-03 04:09</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 06 close to Aug 07 close  |  503 companies  |  updated 2026-08-08 04:05</t>
+          <t>Aug 06 close to Aug 07 close  |  503 companies  |  updated 2026-08-09 04:10</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 31 close to Aug 07 close  |  503 companies  |  updated 2026-08-08 04:05</t>
+          <t>Jul 31 close to Aug 07 close  |  503 companies  |  updated 2026-08-09 04:10</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Aug 06-&gt;Aug 07) and rolling 5-day  |  updated 2026-08-08 04:05</t>
+          <t>Daily (Aug 06-&gt;Aug 07) and rolling 5-day  |  updated 2026-08-09 04:10</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 06 close to Aug 07 close  |  503 companies  |  updated 2026-08-09 04:10</t>
+          <t>Aug 06 close to Aug 07 close  |  503 companies  |  updated 2026-08-10 04:22</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jul 31 close to Aug 07 close  |  503 companies  |  updated 2026-08-09 04:10</t>
+          <t>Jul 31 close to Aug 07 close  |  503 companies  |  updated 2026-08-10 04:22</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Aug 06-&gt;Aug 07) and rolling 5-day  |  updated 2026-08-09 04:10</t>
+          <t>Daily (Aug 06-&gt;Aug 07) and rolling 5-day  |  updated 2026-08-10 04:22</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 13 close to Aug 14 close  |  503 companies  |  updated 2026-08-16 03:40</t>
+          <t>Aug 13 close to Aug 14 close  |  503 companies  |  updated 2026-08-17 03:41</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 07 close to Aug 14 close  |  503 companies  |  updated 2026-08-16 03:40</t>
+          <t>Aug 07 close to Aug 14 close  |  503 companies  |  updated 2026-08-17 03:41</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Aug 13-&gt;Aug 14) and rolling 5-day  |  updated 2026-08-16 03:40</t>
+          <t>Daily (Aug 13-&gt;Aug 14) and rolling 5-day  |  updated 2026-08-17 03:41</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 20 close to Aug 21 close  |  503 companies  |  updated 2026-08-22 03:34</t>
+          <t>Aug 20 close to Aug 21 close  |  503 companies  |  updated 2026-08-23 03:42</t>
         </is>
       </c>
     </row>
@@ -4278,10 +4278,10 @@
         <v>122.91</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>124.47</v>
+        <v>124.48</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="149">
@@ -5084,7 +5084,7 @@
         <v>251.02</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>253.82</v>
+        <v>253.83</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>1.12</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 14 close to Aug 21 close  |  503 companies  |  updated 2026-08-22 03:34</t>
+          <t>Aug 14 close to Aug 21 close  |  503 companies  |  updated 2026-08-23 03:42</t>
         </is>
       </c>
     </row>
@@ -17372,16 +17372,16 @@
         <v>122.02</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>124.47</v>
+        <v>124.48</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>124.47</v>
+        <v>124.48</v>
       </c>
       <c r="G119" s="5" t="n">
         <v>118.54</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="120">
@@ -19004,10 +19004,10 @@
         <v>251.66</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>253.82</v>
+        <v>253.83</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>253.82</v>
+        <v>253.83</v>
       </c>
       <c r="G170" s="5" t="n">
         <v>241.64</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Aug 20-&gt;Aug 21) and rolling 5-day  |  updated 2026-08-22 03:34</t>
+          <t>Daily (Aug 20-&gt;Aug 21) and rolling 5-day  |  updated 2026-08-23 03:42</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 20 close to Aug 21 close  |  503 companies  |  updated 2026-08-23 03:42</t>
+          <t>Aug 20 close to Aug 21 close  |  503 companies  |  updated 2026-08-24 03:45</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 14 close to Aug 21 close  |  503 companies  |  updated 2026-08-23 03:42</t>
+          <t>Aug 14 close to Aug 21 close  |  503 companies  |  updated 2026-08-24 03:45</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Aug 20-&gt;Aug 21) and rolling 5-day  |  updated 2026-08-23 03:42</t>
+          <t>Daily (Aug 20-&gt;Aug 21) and rolling 5-day  |  updated 2026-08-24 03:45</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 27 close to Aug 28 close  |  503 companies  |  updated 2026-08-30 08:42</t>
+          <t>Aug 27 close to Aug 28 close  |  503 companies  |  updated 2026-08-31 09:05</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 21 close to Aug 28 close  |  503 companies  |  updated 2026-08-30 08:42</t>
+          <t>Aug 21 close to Aug 28 close  |  503 companies  |  updated 2026-08-31 09:05</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Aug 27-&gt;Aug 28) and rolling 5-day  |  updated 2026-08-30 08:42</t>
+          <t>Daily (Aug 27-&gt;Aug 28) and rolling 5-day  |  updated 2026-08-31 09:05</t>
         </is>
       </c>
     </row>
